--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannbn/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79ED3FA-4632-4E49-813F-E19768611E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7F39E6-2932-FF4A-94A7-66DEED9BC011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="877" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1261,9 +1261,6 @@
     <t>Operation Mode</t>
   </si>
   <si>
-    <t>Autonomous</t>
-  </si>
-  <si>
     <t>Reactors Monitored Per Operator</t>
   </si>
   <si>
@@ -2255,6 +2252,9 @@
   </si>
   <si>
     <t>Moderator Booster Mass YHx</t>
+  </si>
+  <si>
+    <t>Remotely Monitored</t>
   </si>
 </sst>
 </file>
@@ -2961,21 +2961,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2983,8 +2983,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3009,14 +3009,14 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3056,30 +3056,9 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3092,197 +3071,6 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3341,6 +3129,138 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -3356,6 +3276,86 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3435,13 +3435,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -3456,26 +3449,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3499,9 +3480,14 @@
       </font>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3529,82 +3515,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3651,7 +3562,89 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3673,6 +3666,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3707,7 +3707,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3721,7 +3721,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3793,9 +3793,166 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray125"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray125"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -3812,17 +3969,31 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
       <fill>
-        <patternFill patternType="gray125"/>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -3877,60 +4048,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
@@ -3946,46 +4063,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4025,20 +4102,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i/>
@@ -4046,11 +4109,6 @@
       <fill>
         <patternFill patternType="gray125"/>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4074,11 +4132,9 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4097,63 +4153,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4218,13 +4218,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -4235,18 +4228,6 @@
           <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4284,9 +4265,21 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4303,6 +4296,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
@@ -4315,7 +4315,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4343,42 +4371,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4413,7 +4406,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4425,14 +4418,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4500,9 +4493,23 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -4515,13 +4522,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4553,7 +4553,21 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4567,7 +4581,61 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4589,32 +4657,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4650,48 +4692,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4771,6 +4771,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -4804,6 +4811,58 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -4826,20 +4885,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4870,18 +4915,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
@@ -4891,66 +4924,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5007,9 +4981,42 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -5031,13 +5038,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
@@ -5055,7 +5055,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5069,7 +5069,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5627,7 +5627,7 @@
       <c r="S3" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="145" t="s">
+      <c r="T3" s="141" t="s">
         <v>41</v>
       </c>
       <c r="U3" s="148" t="s">
@@ -6252,13 +6252,13 @@
       <c r="R11" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="145" t="s">
+      <c r="S11" s="141" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="145" t="s">
+      <c r="T11" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="144" t="s">
+      <c r="U11" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="49"/>
@@ -6575,13 +6575,13 @@
       <c r="R15" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S15" s="145" t="s">
+      <c r="S15" s="141" t="s">
         <v>74</v>
       </c>
-      <c r="T15" s="145" t="s">
+      <c r="T15" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U15" s="144" t="s">
+      <c r="U15" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V15" s="49"/>
@@ -7121,13 +7121,13 @@
       <c r="R22" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S22" s="145" t="s">
+      <c r="S22" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="T22" s="145" t="s">
+      <c r="T22" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U22" s="144" t="s">
+      <c r="U22" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V22" s="49"/>
@@ -7430,13 +7430,13 @@
       <c r="R26" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S26" s="145" t="s">
+      <c r="S26" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="T26" s="145" t="s">
+      <c r="T26" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U26" s="144" t="s">
+      <c r="U26" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V26" s="49"/>
@@ -7747,13 +7747,13 @@
       <c r="R30" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S30" s="145" t="s">
+      <c r="S30" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="T30" s="145" t="s">
+      <c r="T30" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U30" s="144" t="s">
+      <c r="U30" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V30" s="49"/>
@@ -8254,13 +8254,13 @@
       <c r="R37" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S37" s="145" t="s">
+      <c r="S37" s="141" t="s">
         <v>74</v>
       </c>
-      <c r="T37" s="145" t="s">
+      <c r="T37" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U37" s="144" t="s">
+      <c r="U37" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V37" s="49"/>
@@ -8561,13 +8561,13 @@
       <c r="R41" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S41" s="145" t="s">
+      <c r="S41" s="141" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="145" t="s">
+      <c r="T41" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U41" s="144" t="s">
+      <c r="U41" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V41" s="49"/>
@@ -8922,13 +8922,13 @@
       <c r="R46" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S46" s="145" t="s">
+      <c r="S46" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="T46" s="145" t="s">
+      <c r="T46" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U46" s="144" t="s">
+      <c r="U46" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V46" s="49"/>
@@ -9373,16 +9373,16 @@
       <c r="R52" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S52" s="145" t="s">
+      <c r="S52" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="T52" s="145" t="s">
+      <c r="T52" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="144" t="s">
+      <c r="U52" s="146" t="s">
         <v>76</v>
       </c>
-      <c r="V52" s="150" t="s">
+      <c r="V52" s="147" t="s">
         <v>162</v>
       </c>
       <c r="W52" s="77" t="s">
@@ -9729,13 +9729,13 @@
       <c r="R57" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S57" s="145" t="s">
+      <c r="S57" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="T57" s="145" t="s">
+      <c r="T57" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="144" t="s">
+      <c r="U57" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="49"/>
@@ -10038,13 +10038,13 @@
       <c r="R61" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S61" s="145" t="s">
+      <c r="S61" s="141" t="s">
         <v>74</v>
       </c>
-      <c r="T61" s="145" t="s">
+      <c r="T61" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="U61" s="144" t="s">
+      <c r="U61" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V61" s="49"/>
@@ -10542,7 +10542,7 @@
       <c r="S68" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="T68" s="146" t="s">
+      <c r="T68" s="144" t="s">
         <v>197</v>
       </c>
       <c r="U68" s="56"/>
@@ -11223,10 +11223,10 @@
       <c r="S76" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="T76" s="146" t="s">
+      <c r="T76" s="144" t="s">
         <v>210</v>
       </c>
-      <c r="U76" s="147" t="s">
+      <c r="U76" s="150" t="s">
         <v>211</v>
       </c>
       <c r="V76" s="59" t="s">
@@ -12141,7 +12141,7 @@
       <c r="T86" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="U86" s="147" t="s">
+      <c r="U86" s="150" t="s">
         <v>211</v>
       </c>
       <c r="V86" s="49"/>
@@ -13478,7 +13478,7 @@
         <v>35</v>
       </c>
       <c r="F101" s="39" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G101" s="39" t="s">
         <v>229</v>
@@ -13492,7 +13492,7 @@
         <v>186</v>
       </c>
       <c r="M101" s="59" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="O101" s="49" t="s">
         <v>188</v>
@@ -13565,7 +13565,7 @@
         <v>35</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G102" s="39" t="s">
         <v>258</v>
@@ -13579,7 +13579,7 @@
         <v>186</v>
       </c>
       <c r="M102" s="59" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O102" s="49" t="s">
         <v>188</v>
@@ -13650,7 +13650,7 @@
         <v>35</v>
       </c>
       <c r="F103" s="39" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G103" s="39" t="s">
         <v>255</v>
@@ -13664,7 +13664,7 @@
         <v>186</v>
       </c>
       <c r="M103" s="59" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="O103" s="49" t="s">
         <v>188</v>
@@ -13873,13 +13873,13 @@
       <c r="S106" s="59" t="s">
         <v>268</v>
       </c>
-      <c r="T106" s="146" t="s">
+      <c r="T106" s="144" t="s">
         <v>269</v>
       </c>
       <c r="U106" s="149" t="s">
         <v>270</v>
       </c>
-      <c r="V106" s="146"/>
+      <c r="V106" s="144"/>
       <c r="W106" s="77" t="s">
         <v>157</v>
       </c>
@@ -15164,7 +15164,7 @@
         <v>292</v>
       </c>
       <c r="U120" s="83"/>
-      <c r="V120" s="146" t="s">
+      <c r="V120" s="144" t="s">
         <v>307</v>
       </c>
       <c r="W120" s="77" t="s">
@@ -16284,10 +16284,10 @@
       <c r="R135" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S135" s="141" t="s">
+      <c r="S135" s="145" t="s">
         <v>340</v>
       </c>
-      <c r="T135" s="141" t="s">
+      <c r="T135" s="145" t="s">
         <v>341</v>
       </c>
       <c r="U135" s="49"/>
@@ -16854,10 +16854,10 @@
       <c r="R142" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S142" s="146" t="s">
+      <c r="S142" s="144" t="s">
         <v>350</v>
       </c>
-      <c r="T142" s="146" t="s">
+      <c r="T142" s="144" t="s">
         <v>351</v>
       </c>
       <c r="U142" s="49"/>
@@ -17626,7 +17626,7 @@
       <c r="R152" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="S152" s="145" t="s">
+      <c r="S152" s="141" t="s">
         <v>316</v>
       </c>
       <c r="T152" s="46"/>
@@ -18327,7 +18327,7 @@
         <v>386</v>
       </c>
       <c r="G163" s="39" t="s">
-        <v>387</v>
+        <v>715</v>
       </c>
       <c r="H163" s="39"/>
       <c r="I163" s="39"/>
@@ -18339,7 +18339,7 @@
         <v>382</v>
       </c>
       <c r="M163" s="59" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N163" s="49"/>
       <c r="O163" s="49"/>
@@ -18405,7 +18405,7 @@
         <v>2</v>
       </c>
       <c r="C164" s="56" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D164" s="39" t="str">
         <f t="shared" si="43"/>
@@ -18426,7 +18426,7 @@
         <v>382</v>
       </c>
       <c r="M164" s="59" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N164" s="49"/>
       <c r="O164" s="49"/>
@@ -18492,7 +18492,7 @@
         <v>1</v>
       </c>
       <c r="C165" s="56" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D165" s="39" t="str">
         <f t="shared" si="43"/>
@@ -18562,7 +18562,7 @@
         <v>186</v>
       </c>
       <c r="M166" s="59" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="N166" s="49"/>
       <c r="O166" s="49" t="s">
@@ -18666,7 +18666,7 @@
         <v>186</v>
       </c>
       <c r="M167" s="59" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="N167" s="49"/>
       <c r="O167" s="49" t="s">
@@ -18680,12 +18680,12 @@
         <v>219</v>
       </c>
       <c r="S167" s="59" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="T167" s="63"/>
       <c r="U167" s="83"/>
       <c r="V167" s="49" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="W167" s="77" t="s">
         <v>43</v>
@@ -18741,7 +18741,7 @@
         <v>1</v>
       </c>
       <c r="C168" s="56" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D168" s="39" t="str">
         <f t="shared" si="43"/>
@@ -18771,13 +18771,13 @@
         <v>53</v>
       </c>
       <c r="S168" s="59" t="s">
+        <v>395</v>
+      </c>
+      <c r="T168" s="63" t="s">
         <v>396</v>
       </c>
-      <c r="T168" s="63" t="s">
-        <v>397</v>
-      </c>
       <c r="U168" s="83" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="V168" s="49"/>
       <c r="W168" s="3" t="s">
@@ -18811,7 +18811,7 @@
         <v>1</v>
       </c>
       <c r="C169" s="56" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D169" s="39" t="str">
         <f t="shared" si="43"/>
@@ -18832,14 +18832,14 @@
       <c r="Q169" s="66"/>
       <c r="R169" s="49"/>
       <c r="S169" s="59" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="T169" s="59" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="U169" s="49"/>
       <c r="V169" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="W169" s="77"/>
       <c r="X169" s="80"/>
@@ -18862,7 +18862,7 @@
         <v>2</v>
       </c>
       <c r="C170" s="56" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D170" s="39" t="str">
         <f t="shared" si="43"/>
@@ -18882,15 +18882,15 @@
       <c r="P170" s="49"/>
       <c r="Q170" s="66"/>
       <c r="R170" s="49"/>
-      <c r="S170" s="146" t="s">
+      <c r="S170" s="144" t="s">
+        <v>398</v>
+      </c>
+      <c r="T170" s="144" t="s">
+        <v>398</v>
+      </c>
+      <c r="U170" s="49"/>
+      <c r="V170" s="144" t="s">
         <v>399</v>
-      </c>
-      <c r="T170" s="146" t="s">
-        <v>399</v>
-      </c>
-      <c r="U170" s="49"/>
-      <c r="V170" s="146" t="s">
-        <v>400</v>
       </c>
       <c r="W170" s="77"/>
       <c r="X170" s="80"/>
@@ -18913,7 +18913,7 @@
         <v>2</v>
       </c>
       <c r="C171" s="56" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D171" s="39" t="str">
         <f t="shared" si="43"/>
@@ -18958,7 +18958,7 @@
         <v>2</v>
       </c>
       <c r="C172" s="56" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D172" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19003,7 +19003,7 @@
         <v>2</v>
       </c>
       <c r="C173" s="56" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D173" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19048,7 +19048,7 @@
         <v>2</v>
       </c>
       <c r="C174" s="56" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D174" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19093,7 +19093,7 @@
         <v>2</v>
       </c>
       <c r="C175" s="56" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D175" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19138,7 +19138,7 @@
         <v>2</v>
       </c>
       <c r="C176" s="56" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D176" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19190,7 +19190,7 @@
         <v>1</v>
       </c>
       <c r="C177" s="56" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D177" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19214,7 +19214,7 @@
       <c r="T177" s="59"/>
       <c r="U177" s="49"/>
       <c r="V177" s="59" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="W177" s="77"/>
       <c r="X177" s="80"/>
@@ -19244,7 +19244,7 @@
         <v>0</v>
       </c>
       <c r="C178" s="71" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D178" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19296,7 +19296,7 @@
         <v>1</v>
       </c>
       <c r="C179" s="56" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D179" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19390,7 +19390,7 @@
         <v>1</v>
       </c>
       <c r="C180" s="56" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D180" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19442,7 +19442,7 @@
         <v>1</v>
       </c>
       <c r="C181" s="56" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D181" s="39" t="str">
         <f t="shared" si="43"/>
@@ -19460,10 +19460,10 @@
         <v>1</v>
       </c>
       <c r="L181" s="49" t="s">
+        <v>413</v>
+      </c>
+      <c r="M181" s="59" t="s">
         <v>414</v>
-      </c>
-      <c r="M181" s="59" t="s">
-        <v>415</v>
       </c>
       <c r="N181" s="49"/>
       <c r="O181" s="49"/>
@@ -19521,11 +19521,38 @@
   </sheetData>
   <autoFilter ref="A1:AB181" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="53">
-    <mergeCell ref="T26:T28"/>
-    <mergeCell ref="T41:T43"/>
-    <mergeCell ref="V106:V107"/>
-    <mergeCell ref="T61:T63"/>
-    <mergeCell ref="T76:T80"/>
+    <mergeCell ref="T135:T140"/>
+    <mergeCell ref="U30:U32"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="T170:T176"/>
+    <mergeCell ref="U15:U17"/>
+    <mergeCell ref="U46:U48"/>
+    <mergeCell ref="S142:S147"/>
+    <mergeCell ref="U41:U43"/>
+    <mergeCell ref="S61:S63"/>
+    <mergeCell ref="U61:U63"/>
+    <mergeCell ref="U57:U59"/>
+    <mergeCell ref="S170:S176"/>
+    <mergeCell ref="U76:U80"/>
+    <mergeCell ref="S57:S59"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="U86:U96"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T15:T17"/>
+    <mergeCell ref="S41:S43"/>
+    <mergeCell ref="U106:U107"/>
+    <mergeCell ref="T68:T73"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S22:S24"/>
+    <mergeCell ref="U22:U24"/>
+    <mergeCell ref="T30:T32"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="U37:U39"/>
+    <mergeCell ref="T106:T107"/>
     <mergeCell ref="S135:S140"/>
     <mergeCell ref="T11:T13"/>
     <mergeCell ref="V170:V176"/>
@@ -19542,48 +19569,21 @@
     <mergeCell ref="S152:S155"/>
     <mergeCell ref="T142:T147"/>
     <mergeCell ref="V52:V54"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T15:T17"/>
-    <mergeCell ref="S41:S43"/>
-    <mergeCell ref="U106:U107"/>
-    <mergeCell ref="T68:T73"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S22:S24"/>
-    <mergeCell ref="U22:U24"/>
-    <mergeCell ref="T30:T32"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="U37:U39"/>
-    <mergeCell ref="T106:T107"/>
-    <mergeCell ref="T135:T140"/>
-    <mergeCell ref="U30:U32"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="T170:T176"/>
-    <mergeCell ref="U15:U17"/>
-    <mergeCell ref="U46:U48"/>
-    <mergeCell ref="S142:S147"/>
-    <mergeCell ref="U41:U43"/>
-    <mergeCell ref="S61:S63"/>
-    <mergeCell ref="U61:U63"/>
-    <mergeCell ref="U57:U59"/>
-    <mergeCell ref="S170:S176"/>
-    <mergeCell ref="U76:U80"/>
-    <mergeCell ref="S57:S59"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="U86:U96"/>
+    <mergeCell ref="T26:T28"/>
+    <mergeCell ref="T41:T43"/>
+    <mergeCell ref="V106:V107"/>
+    <mergeCell ref="T61:T63"/>
+    <mergeCell ref="T76:T80"/>
   </mergeCells>
   <conditionalFormatting sqref="A97:B103">
-    <cfRule type="expression" dxfId="301" priority="574">
-      <formula>$B97&lt;2</formula>
+    <cfRule type="expression" dxfId="301" priority="572">
+      <formula>$B97=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="300" priority="573">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="299" priority="572">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="299" priority="574">
+      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106:F108 U113:V119 U120:U121 A135:B140 N142:V142 N143:R143 U143:V148 K144:R144 A148:T148 T152:V157 A158:V161 A162:J163">
@@ -19602,17 +19602,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A150:R157">
-    <cfRule type="expression" dxfId="295" priority="682">
-      <formula>$B150=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="294" priority="681">
+    <cfRule type="expression" dxfId="295" priority="681">
       <formula>$B150=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="293" priority="684">
+    <cfRule type="expression" dxfId="294" priority="684">
       <formula>$B150=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="292" priority="683">
+    <cfRule type="expression" dxfId="293" priority="683">
       <formula>$B150&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="292" priority="682">
+      <formula>$B150=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A124:S125 U124:V125 U166:V168">
@@ -19621,28 +19621,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105:U105">
-    <cfRule type="expression" dxfId="290" priority="790">
+    <cfRule type="expression" dxfId="290" priority="792">
+      <formula>$B105=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="289" priority="791">
+      <formula>$B105&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="288" priority="790">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="289" priority="789">
+    <cfRule type="expression" dxfId="287" priority="789">
       <formula>$B105=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="288" priority="791">
-      <formula>$B105&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="287" priority="792">
-      <formula>$B105=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74:V96 A104:V104 A170:R176">
-    <cfRule type="expression" dxfId="286" priority="488">
-      <formula>$B74&lt;2</formula>
+    <cfRule type="expression" dxfId="286" priority="487">
+      <formula>$B74=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="285" priority="486">
       <formula>$B74=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="284" priority="487">
-      <formula>$B74=2</formula>
+    <cfRule type="expression" dxfId="284" priority="488">
+      <formula>$B74&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:V83">
@@ -19676,39 +19676,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A149:V149">
-    <cfRule type="expression" dxfId="277" priority="720">
-      <formula>$B149=0</formula>
+    <cfRule type="expression" dxfId="277" priority="717">
+      <formula>$B149=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="276" priority="719">
+    <cfRule type="expression" dxfId="276" priority="718">
+      <formula>$B149=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="275" priority="719">
       <formula>$B149&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="275" priority="718">
-      <formula>$B149=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="274" priority="717">
-      <formula>$B149=3</formula>
+    <cfRule type="expression" dxfId="274" priority="720">
+      <formula>$B149=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178:V181">
-    <cfRule type="expression" dxfId="273" priority="651">
-      <formula>$B178&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="272" priority="649">
+    <cfRule type="expression" dxfId="273" priority="649">
       <formula>$B178=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="271" priority="650">
+    <cfRule type="expression" dxfId="272" priority="650">
       <formula>$B178=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="271" priority="651">
+      <formula>$B178&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="270" priority="652">
       <formula>$B178=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A106:F108 A109:V111 U113:V119 U120:U121 A124:S125 U124:V125 A135:B140 U135:V140 A141:V141 N142:V142 N143:R143 U143:V148 K144:R144 A148:T148 T152:V157 A158:V161 A162:J163 A164:L168 U166:V168">
-    <cfRule type="expression" dxfId="269" priority="786">
+    <cfRule type="expression" dxfId="269" priority="787">
+      <formula>$B1&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="268" priority="786">
       <formula>$B1=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="268" priority="787">
-      <formula>$B1&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG51 A170:R176">
@@ -19720,11 +19720,11 @@
     <cfRule type="expression" dxfId="266" priority="551">
       <formula>$B7=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="265" priority="553">
+    <cfRule type="expression" dxfId="265" priority="552">
+      <formula>$B7=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="264" priority="553">
       <formula>$B7&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="264" priority="552">
-      <formula>$B7=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG84 A97:B103 A109:AG120 A121:U121 W121:AG121 A122:AG131 A132:V132 A133:Y133 A134:AG134 S170:AG170 U171:U176 W171:AG176 A177:AG181 A94:AG94">
@@ -19743,25 +19743,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85:AG85">
-    <cfRule type="expression" dxfId="260" priority="63">
-      <formula>$B85&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="259" priority="61">
+    <cfRule type="expression" dxfId="260" priority="61">
       <formula>$B85=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="258" priority="62">
+    <cfRule type="expression" dxfId="259" priority="62">
       <formula>$B85=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="258" priority="63">
+      <formula>$B85&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A86:AG93">
-    <cfRule type="expression" dxfId="257" priority="524">
-      <formula>$B86&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="256" priority="522">
+    <cfRule type="expression" dxfId="257" priority="522">
       <formula>$B86=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="255" priority="523">
+    <cfRule type="expression" dxfId="256" priority="523">
       <formula>$B86=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="255" priority="524">
+      <formula>$B86&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A94:AG96 D97:D103 A145:G146 I145:R146 A147:R147">
@@ -19810,11 +19810,11 @@
     <cfRule type="expression" dxfId="244" priority="419">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="243" priority="420">
+    <cfRule type="expression" dxfId="243" priority="421">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="242" priority="420">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="242" priority="421">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C99:C102">
@@ -19829,39 +19829,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101:C103">
-    <cfRule type="expression" dxfId="238" priority="405">
-      <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="237" priority="407">
+    <cfRule type="expression" dxfId="238" priority="407">
       <formula>$B101&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="236" priority="406">
+    <cfRule type="expression" dxfId="237" priority="406">
       <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="236" priority="405">
+      <formula>$B101=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102:C103">
     <cfRule type="expression" dxfId="235" priority="53">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="234" priority="52">
+    <cfRule type="expression" dxfId="234" priority="51">
+      <formula>$B102=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="233" priority="52">
       <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="233" priority="51">
-      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C135:T135 C136:R140">
-    <cfRule type="expression" dxfId="232" priority="609">
+    <cfRule type="expression" dxfId="232" priority="608">
+      <formula>$B135=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="231" priority="609">
       <formula>$B135=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="231" priority="611">
-      <formula>$B135=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="230" priority="610">
       <formula>$B135&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="229" priority="608">
-      <formula>$B135=3</formula>
+    <cfRule type="expression" dxfId="229" priority="611">
+      <formula>$B135=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D80 D82 D84:D134 D141:D181">
@@ -19905,25 +19905,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D97:E103">
-    <cfRule type="expression" dxfId="228" priority="400">
-      <formula>$B97&lt;2</formula>
+    <cfRule type="expression" dxfId="228" priority="398">
+      <formula>$B97=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="227" priority="399">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="226" priority="398">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="226" priority="400">
+      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E97:E103">
     <cfRule type="expression" dxfId="225" priority="395">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="224" priority="397">
+    <cfRule type="expression" dxfId="224" priority="396">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="223" priority="397">
       <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="223" priority="396">
-      <formula>$B97=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E83:Q83 Q124:Q125">
@@ -19942,14 +19942,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103">
-    <cfRule type="expression" dxfId="219" priority="20">
-      <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="218" priority="21">
+    <cfRule type="expression" dxfId="219" priority="21">
       <formula>$B103=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="217" priority="22">
+    <cfRule type="expression" dxfId="218" priority="22">
       <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="217" priority="20">
+      <formula>$B103=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109:F111">
@@ -19958,36 +19958,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111">
-    <cfRule type="expression" dxfId="215" priority="69">
+    <cfRule type="expression" dxfId="215" priority="68">
+      <formula>$B111=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="214" priority="69">
       <formula>$B111=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="214" priority="70">
+    <cfRule type="expression" dxfId="213" priority="70">
       <formula>$B111&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="213" priority="68">
-      <formula>$B111=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102:G102">
-    <cfRule type="expression" dxfId="212" priority="25">
+    <cfRule type="expression" dxfId="212" priority="23">
+      <formula>$B102=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="211" priority="25">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="211" priority="24">
+    <cfRule type="expression" dxfId="210" priority="24">
       <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="210" priority="23">
-      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109:G110">
-    <cfRule type="expression" dxfId="209" priority="72">
+    <cfRule type="expression" dxfId="209" priority="71">
+      <formula>$B109=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="208" priority="72">
       <formula>$B109=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="208" priority="73">
+    <cfRule type="expression" dxfId="207" priority="73">
       <formula>$B109&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="207" priority="71">
-      <formula>$B109=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51:I54">
@@ -19997,63 +19997,63 @@
     <cfRule type="expression" dxfId="205" priority="557">
       <formula>$B51=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="204" priority="559">
+    <cfRule type="expression" dxfId="204" priority="558">
+      <formula>$B51&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="203" priority="559">
       <formula>$B51=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="203" priority="558">
-      <formula>$B51&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97:I98">
-    <cfRule type="expression" dxfId="202" priority="379">
+    <cfRule type="expression" dxfId="202" priority="378">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="201" priority="379">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="201" priority="377">
+    <cfRule type="expression" dxfId="200" priority="377">
       <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="200" priority="378">
-      <formula>$B97=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97:I99 F100 H100:I100 F101:I101 H102:I102 F102:F103">
-    <cfRule type="expression" dxfId="199" priority="189">
+    <cfRule type="expression" dxfId="199" priority="188">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="198" priority="189">
       <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="198" priority="188">
-      <formula>$B97=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99:I101">
     <cfRule type="expression" dxfId="197" priority="59">
       <formula>$B99&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="58">
+    <cfRule type="expression" dxfId="196" priority="57">
+      <formula>$B99=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="195" priority="58">
       <formula>$B99=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="195" priority="57">
-      <formula>$B99=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102:I103">
-    <cfRule type="expression" dxfId="194" priority="34">
-      <formula>$B102&lt;2</formula>
+    <cfRule type="expression" dxfId="194" priority="32">
+      <formula>$B102=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="193" priority="33">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="32">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="192" priority="34">
+      <formula>$B102&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103:I103">
-    <cfRule type="expression" dxfId="191" priority="181">
+    <cfRule type="expression" dxfId="191" priority="182">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="190" priority="181">
       <formula>$B103=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="180">
+    <cfRule type="expression" dxfId="189" priority="180">
       <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="189" priority="182">
-      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:U54 W53:AG54 A55:AG75 A104:AG105 A106:V109 A109:AG120 A121:U121 W121:AG121 A122:AG131 A126:V141 S170:AG170 U171:U176 W171:AG176 A177:AG181">
@@ -20067,50 +20067,50 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G100">
-    <cfRule type="expression" dxfId="186" priority="55">
+    <cfRule type="expression" dxfId="186" priority="56">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="185" priority="55">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="54">
+    <cfRule type="expression" dxfId="184" priority="54">
       <formula>$B100=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="184" priority="56">
-      <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G106:I107">
-    <cfRule type="expression" dxfId="183" priority="781">
-      <formula>$B106=3</formula>
+    <cfRule type="expression" dxfId="183" priority="784">
+      <formula>$B106=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="782">
+    <cfRule type="expression" dxfId="182" priority="783">
+      <formula>$B106&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="181" priority="782">
       <formula>$B106=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="783">
-      <formula>$B106&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="180" priority="784">
-      <formula>$B106=0</formula>
+    <cfRule type="expression" dxfId="180" priority="781">
+      <formula>$B106=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H145:H146 K162:L163">
-    <cfRule type="expression" dxfId="179" priority="667">
+    <cfRule type="expression" dxfId="179" priority="666">
+      <formula>$B146=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="178" priority="667">
       <formula>$B146&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="668">
+    <cfRule type="expression" dxfId="177" priority="668">
       <formula>$B146=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="177" priority="666">
-      <formula>$B146=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H145:H146">
-    <cfRule type="expression" dxfId="176" priority="1059">
+    <cfRule type="expression" dxfId="176" priority="1057">
+      <formula>$B146&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="175" priority="1059">
       <formula>$B146=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="175" priority="1056">
+    <cfRule type="expression" dxfId="174" priority="1056">
       <formula>$B146=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="174" priority="1057">
-      <formula>$B146&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5">
@@ -20146,14 +20146,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69:S73">
-    <cfRule type="expression" dxfId="165" priority="634">
+    <cfRule type="expression" dxfId="165" priority="636">
+      <formula>$B69&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="164" priority="634">
       <formula>$B69=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="635">
+    <cfRule type="expression" dxfId="163" priority="635">
       <formula>$B69=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="163" priority="636">
-      <formula>$B69&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:V68 J69:S70 U69:V73">
@@ -20162,14 +20162,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:V68 U69:V73">
-    <cfRule type="expression" dxfId="161" priority="644">
-      <formula>$B68=3</formula>
+    <cfRule type="expression" dxfId="161" priority="646">
+      <formula>$B68&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="160" priority="645">
       <formula>$B68=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="159" priority="646">
-      <formula>$B68&lt;2</formula>
+    <cfRule type="expression" dxfId="159" priority="644">
+      <formula>$B68=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81">
@@ -20183,25 +20183,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:M98">
-    <cfRule type="expression" dxfId="156" priority="331">
+    <cfRule type="expression" dxfId="156" priority="333">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="155" priority="331">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="155" priority="332">
+    <cfRule type="expression" dxfId="154" priority="332">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="154" priority="333">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:M101">
-    <cfRule type="expression" dxfId="153" priority="159">
-      <formula>$B97&lt;2</formula>
+    <cfRule type="expression" dxfId="153" priority="157">
+      <formula>$B97=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="152" priority="158">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="151" priority="157">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="151" priority="159">
+      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:M103">
@@ -20213,11 +20213,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:M103">
-    <cfRule type="expression" dxfId="148" priority="151">
+    <cfRule type="expression" dxfId="148" priority="150">
+      <formula>$B99=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="147" priority="151">
       <formula>$B99&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="147" priority="150">
-      <formula>$B99=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="146" priority="149">
       <formula>$B99=3</formula>
@@ -20227,11 +20227,11 @@
     <cfRule type="expression" dxfId="145" priority="50">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="48">
+    <cfRule type="expression" dxfId="144" priority="49">
+      <formula>$B102=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="143" priority="48">
       <formula>$B102=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="143" priority="49">
-      <formula>$B102=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K103:M103">
@@ -20246,56 +20246,56 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K142:M143">
-    <cfRule type="expression" dxfId="139" priority="748">
-      <formula>$B142=0</formula>
+    <cfRule type="expression" dxfId="139" priority="746">
+      <formula>$B142=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="138" priority="747">
       <formula>$B142&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="746">
-      <formula>$B142=2</formula>
+    <cfRule type="expression" dxfId="137" priority="745">
+      <formula>$B142=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="745">
-      <formula>$B142=3</formula>
+    <cfRule type="expression" dxfId="136" priority="748">
+      <formula>$B142=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112">
-    <cfRule type="expression" dxfId="135" priority="984">
+    <cfRule type="expression" dxfId="135" priority="987">
+      <formula>#REF!=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="134" priority="986">
+      <formula>#REF!=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="133" priority="985">
+      <formula>#REF!&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="132" priority="984">
       <formula>#REF!=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="985">
-      <formula>#REF!&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="133" priority="594">
+    <cfRule type="expression" dxfId="131" priority="594">
       <formula>$B112=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="132" priority="986">
-      <formula>#REF!=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="131" priority="987">
-      <formula>#REF!=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112:V112">
     <cfRule type="expression" dxfId="130" priority="593">
       <formula>$B112&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="591">
+    <cfRule type="expression" dxfId="129" priority="592">
+      <formula>$B112=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="128" priority="591">
       <formula>$B112=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="128" priority="592">
-      <formula>$B112=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M102:M103">
-    <cfRule type="expression" dxfId="127" priority="18">
+    <cfRule type="expression" dxfId="127" priority="17">
+      <formula>$B102=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="126" priority="18">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="19">
+    <cfRule type="expression" dxfId="125" priority="19">
       <formula>$B102&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="125" priority="17">
-      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N81">
@@ -20304,42 +20304,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O97:O98">
-    <cfRule type="expression" dxfId="123" priority="316">
-      <formula>$B97=2</formula>
+    <cfRule type="expression" dxfId="123" priority="315">
+      <formula>$B97=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="122" priority="317">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="315">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="121" priority="316">
+      <formula>$B97=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O97:O103">
-    <cfRule type="expression" dxfId="120" priority="309">
+    <cfRule type="expression" dxfId="120" priority="310">
+      <formula>$B97=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="119" priority="309">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="119" priority="308">
+    <cfRule type="expression" dxfId="118" priority="308">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="307">
+    <cfRule type="expression" dxfId="117" priority="307">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="306">
+    <cfRule type="expression" dxfId="116" priority="306">
       <formula>_xlfn.ISFORMULA(O97)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="116" priority="310">
-      <formula>$B97=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O99:O103">
     <cfRule type="expression" dxfId="115" priority="305">
       <formula>$B99&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="303">
+    <cfRule type="expression" dxfId="114" priority="304">
+      <formula>$B99=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="303">
       <formula>$B99=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="304">
-      <formula>$B99=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71:Q73">
@@ -20378,14 +20378,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:R100">
-    <cfRule type="expression" dxfId="103" priority="276">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="103" priority="278">
+      <formula>$B97&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="102" priority="277">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="278">
-      <formula>$B97&lt;2</formula>
+    <cfRule type="expression" dxfId="101" priority="276">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:R101">
@@ -20403,19 +20403,19 @@
     <cfRule type="expression" dxfId="97" priority="45">
       <formula>$B102=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="46">
+    <cfRule type="expression" dxfId="96" priority="47">
+      <formula>$B102&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="95" priority="46">
       <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="47">
-      <formula>$B102&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q103:R103">
-    <cfRule type="expression" dxfId="94" priority="119">
+    <cfRule type="expression" dxfId="94" priority="120">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="119">
       <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="120">
-      <formula>$B103&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="92" priority="118">
       <formula>$B103=3</formula>
@@ -20427,25 +20427,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q99:S100">
-    <cfRule type="expression" dxfId="90" priority="269">
+    <cfRule type="expression" dxfId="90" priority="271">
+      <formula>$B99&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="269">
       <formula>$B99=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="270">
+    <cfRule type="expression" dxfId="88" priority="270">
       <formula>$B99=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="271">
-      <formula>$B99&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:S101">
-    <cfRule type="expression" dxfId="87" priority="106">
-      <formula>$B101&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="104">
+    <cfRule type="expression" dxfId="87" priority="104">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="105">
+    <cfRule type="expression" dxfId="86" priority="105">
       <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="106">
+      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q102:S102">
@@ -20463,11 +20463,11 @@
     <cfRule type="expression" dxfId="81" priority="113">
       <formula>$B103&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="111">
+    <cfRule type="expression" dxfId="80" priority="112">
+      <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="111">
       <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="112">
-      <formula>$B103=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:T103">
@@ -20476,64 +20476,64 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S97:S100">
-    <cfRule type="expression" dxfId="77" priority="264">
-      <formula>$B97&lt;2</formula>
+    <cfRule type="expression" dxfId="77" priority="262">
+      <formula>$B97=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="76" priority="263">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="262">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="75" priority="264">
+      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S102">
-    <cfRule type="expression" dxfId="74" priority="39">
-      <formula>$B102=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="41">
+    <cfRule type="expression" dxfId="74" priority="41">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="40">
+    <cfRule type="expression" dxfId="73" priority="40">
       <formula>$B102=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="39">
+      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S152">
     <cfRule type="expression" dxfId="71" priority="731">
       <formula>$B152&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="732">
-      <formula>$B152=0</formula>
+    <cfRule type="expression" dxfId="70" priority="730">
+      <formula>$B152=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="69" priority="729">
       <formula>$B152=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="730">
-      <formula>$B152=2</formula>
+    <cfRule type="expression" dxfId="68" priority="732">
+      <formula>$B152=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S156:S157">
-    <cfRule type="expression" dxfId="67" priority="725">
+    <cfRule type="expression" dxfId="67" priority="728">
+      <formula>$B156=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="725">
       <formula>$B156=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="726">
+    <cfRule type="expression" dxfId="65" priority="726">
       <formula>$B156=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="728">
-      <formula>$B156=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="64" priority="727">
       <formula>$B156&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S97:T98">
-    <cfRule type="expression" dxfId="63" priority="256">
+    <cfRule type="expression" dxfId="63" priority="255">
+      <formula>$B97=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="256">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="257">
+    <cfRule type="expression" dxfId="61" priority="257">
       <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="255">
-      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S101:T101">
@@ -20578,89 +20578,89 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5">
-    <cfRule type="expression" dxfId="49" priority="484">
-      <formula>$B5=2</formula>
+    <cfRule type="expression" dxfId="49" priority="485">
+      <formula>$B5&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="485">
-      <formula>$B5&lt;2</formula>
+    <cfRule type="expression" dxfId="48" priority="482">
+      <formula>$B5=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="483">
       <formula>$B5=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="482">
-      <formula>$B5=0</formula>
+    <cfRule type="expression" dxfId="46" priority="484">
+      <formula>$B5=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6">
-    <cfRule type="expression" dxfId="45" priority="1040">
-      <formula>$B5=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="1045">
+    <cfRule type="expression" dxfId="45" priority="1045">
       <formula>$B5=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="1043">
+    <cfRule type="expression" dxfId="44" priority="1043">
       <formula>$B5=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="1040">
+      <formula>$B5=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="42" priority="1041">
       <formula>$B5&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T97:T100">
-    <cfRule type="expression" dxfId="41" priority="249">
+    <cfRule type="expression" dxfId="41" priority="248">
+      <formula>$B97=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="249">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="250">
+    <cfRule type="expression" dxfId="39" priority="250">
       <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="248">
-      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T99:T102">
-    <cfRule type="expression" dxfId="38" priority="98">
+    <cfRule type="expression" dxfId="38" priority="97">
+      <formula>$B99=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="98">
       <formula>$B99=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="97">
-      <formula>$B99=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="36" priority="99">
       <formula>$B99&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T100">
-    <cfRule type="expression" dxfId="35" priority="28">
-      <formula>$B100&lt;2</formula>
+    <cfRule type="expression" dxfId="35" priority="26">
+      <formula>$B100=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="34" priority="27">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="26">
-      <formula>$B100=3</formula>
+    <cfRule type="expression" dxfId="33" priority="28">
+      <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T102:T103">
     <cfRule type="expression" dxfId="32" priority="38">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="37">
+    <cfRule type="expression" dxfId="31" priority="36">
+      <formula>$B102=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="37">
       <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="36">
-      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U106">
-    <cfRule type="expression" dxfId="29" priority="813">
+    <cfRule type="expression" dxfId="29" priority="812">
+      <formula>$B105&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="813">
       <formula>$B105=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="812">
-      <formula>$B105&lt;2</formula>
+    <cfRule type="expression" dxfId="27" priority="810">
+      <formula>$B105=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="811">
+    <cfRule type="expression" dxfId="26" priority="811">
       <formula>$B105=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="810">
-      <formula>$B105=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U135:AG140">
@@ -20669,17 +20669,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W97:W103">
-    <cfRule type="expression" dxfId="24" priority="237">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="24" priority="240">
+      <formula>$B97=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="238">
+    <cfRule type="expression" dxfId="23" priority="239">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="238">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="239">
-      <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="240">
-      <formula>$B97=0</formula>
+    <cfRule type="expression" dxfId="21" priority="237">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W76:AG82">
@@ -20697,11 +20697,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W95:AG96 A145:G146 I145:R146 A147:R147">
-    <cfRule type="expression" dxfId="16" priority="734">
+    <cfRule type="expression" dxfId="16" priority="735">
+      <formula>$B95&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="734">
       <formula>$B95=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="735">
-      <formula>$B95&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W106:AG108">
@@ -20713,36 +20713,36 @@
     <cfRule type="expression" dxfId="13" priority="503">
       <formula>$B132=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="505">
+    <cfRule type="expression" dxfId="12" priority="502">
+      <formula>$B132=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="505">
       <formula>$B132=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="502">
-      <formula>$B132=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="504">
       <formula>$B132&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W135:AG140">
-    <cfRule type="expression" dxfId="9" priority="430">
-      <formula>$B135=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="431">
+    <cfRule type="expression" dxfId="9" priority="431">
       <formula>$B135=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="432">
+    <cfRule type="expression" dxfId="8" priority="432">
       <formula>$B135&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="430">
+      <formula>$B135=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z97:AG103">
-    <cfRule type="expression" dxfId="6" priority="82">
-      <formula>$B97=0</formula>
+    <cfRule type="expression" dxfId="6" priority="79">
+      <formula>$B97=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="80">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="79">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="4" priority="82">
+      <formula>$B97=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="81">
       <formula>$B97&lt;2</formula>
@@ -20842,13 +20842,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B1" s="153" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="151" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -20909,7 +20909,7 @@
         <v>211</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C7" s="11"/>
     </row>
@@ -20950,7 +20950,7 @@
         <v>214.7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C11" s="11">
         <v>225536.86</v>
@@ -20962,7 +20962,7 @@
         <v>217</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C12" s="11"/>
     </row>
@@ -20995,7 +20995,7 @@
         <v>221.1</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C15" s="11">
         <f>C16+C17+C18</f>
@@ -21007,7 +21007,7 @@
         <v>221.11</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C16" s="11">
         <v>762382.4</v>
@@ -21018,7 +21018,7 @@
         <v>221.12</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C17" s="11">
         <v>1201688.6000000001</v>
@@ -21029,7 +21029,7 @@
         <v>221.13</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C18" s="11">
         <v>40781</v>
@@ -21040,7 +21040,7 @@
         <v>221.2</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C19" s="11">
         <f>C20</f>
@@ -21052,7 +21052,7 @@
         <v>221.21</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C20" s="11">
         <f>SUM(C21:C23)</f>
@@ -21106,7 +21106,7 @@
         <v>221.3</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C25" s="11">
         <f>C26+C30+C31</f>
@@ -21129,7 +21129,7 @@
         <v>221.31100000000001</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C27" s="11">
         <v>3200000</v>
@@ -21140,7 +21140,7 @@
         <v>221.31200000000001</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C28" s="11">
         <v>850000</v>
@@ -21151,7 +21151,7 @@
         <v>221.31299999999999</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C29" s="11">
         <v>120231</v>
@@ -21181,7 +21181,7 @@
     </row>
     <row r="32" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>261</v>
@@ -21196,7 +21196,7 @@
         <v>222.1</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C33" s="11">
         <v>0</v>
@@ -21207,7 +21207,7 @@
         <v>222.2</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C34" s="11">
         <v>4890230.5999999996</v>
@@ -21218,7 +21218,7 @@
         <v>222.21</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C35" s="11">
         <v>1520786</v>
@@ -21229,7 +21229,7 @@
         <v>222.22</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C36" s="11">
         <v>3341486</v>
@@ -21240,7 +21240,7 @@
         <v>222.23</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C37" s="11">
         <v>27958.6</v>
@@ -21262,7 +21262,7 @@
         <v>222.4</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C39" s="11">
         <v>0</v>
@@ -21273,7 +21273,7 @@
         <v>222.5</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C40" s="11">
         <v>1018720</v>
@@ -21281,16 +21281,16 @@
     </row>
     <row r="41" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="29" t="s">
+        <v>438</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="C41" s="11"/>
     </row>
     <row r="42" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>315</v>
@@ -21301,7 +21301,7 @@
     </row>
     <row r="43" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>323</v>
@@ -21312,7 +21312,7 @@
     </row>
     <row r="44" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>328</v>
@@ -21326,7 +21326,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C45" s="11">
         <f>C46</f>
@@ -21370,10 +21370,10 @@
     </row>
     <row r="49" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="29" t="s">
+        <v>444</v>
+      </c>
+      <c r="B49" s="10" t="s">
         <v>445</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>446</v>
       </c>
       <c r="C49" s="11">
         <v>1627.02</v>
@@ -21381,10 +21381,10 @@
     </row>
     <row r="50" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29" t="s">
+        <v>446</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>447</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>448</v>
       </c>
       <c r="C50" s="11">
         <v>0</v>
@@ -21392,10 +21392,10 @@
     </row>
     <row r="51" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29" t="s">
+        <v>448</v>
+      </c>
+      <c r="B51" s="10" t="s">
         <v>449</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>450</v>
       </c>
       <c r="C51" s="11">
         <v>71788.600000000006</v>
@@ -21415,7 +21415,7 @@
     </row>
     <row r="53" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="29" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>356</v>
@@ -21429,7 +21429,7 @@
         <v>26</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C54" s="11"/>
     </row>
@@ -21450,7 +21450,7 @@
         <v>31</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C56" s="11">
         <f>C57</f>
@@ -21462,7 +21462,7 @@
         <v>317</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C57" s="11">
         <v>1333020.8</v>
@@ -21485,7 +21485,7 @@
         <v>331</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C59" s="11">
         <f>C60+C61</f>
@@ -21497,7 +21497,7 @@
         <v>331.3</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C60" s="11">
         <v>215000</v>
@@ -21508,7 +21508,7 @@
         <v>331.5</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C61" s="11">
         <v>2192166.4</v>
@@ -21531,7 +21531,7 @@
         <v>341</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C63" s="11">
         <v>1635355.8</v>
@@ -21542,7 +21542,7 @@
         <v>345</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C64" s="11">
         <v>29927</v>
@@ -21565,7 +21565,7 @@
         <v>351</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C66" s="11">
         <v>257261.4</v>
@@ -21576,7 +21576,7 @@
         <v>352</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C67" s="11">
         <v>363052.18773783161</v>
@@ -21599,7 +21599,7 @@
         <v>361</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C69" s="11"/>
     </row>
@@ -21608,7 +21608,7 @@
         <v>362</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C70" s="11">
         <v>416958.9359999997</v>
@@ -21619,7 +21619,7 @@
         <v>40</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C71" s="13">
         <f>C72</f>
@@ -21631,7 +21631,7 @@
         <v>41</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C72" s="11">
         <v>4169765</v>
@@ -21642,7 +21642,7 @@
         <v>50</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C73" s="13">
         <f>C74</f>
@@ -21654,7 +21654,7 @@
         <v>54</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C74" s="11">
         <v>16408781.6</v>
@@ -21677,7 +21677,7 @@
         <v>61</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C76" s="11">
         <v>6160606</v>
@@ -21708,10 +21708,10 @@
     </row>
     <row r="79" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C79" s="11">
         <v>33779050.138262168</v>
@@ -21745,21 +21745,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>468</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>469</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="155" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B2" s="156"/>
       <c r="C2" s="156"/>
@@ -21767,56 +21767,56 @@
     </row>
     <row r="3" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B3" s="5">
         <v>83</v>
       </c>
       <c r="C3" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>473</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B4" s="5">
         <v>20</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D4" s="21"/>
     </row>
     <row r="5" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B5" s="5">
         <v>5.5</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B6" s="5">
         <v>16.5</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -21829,58 +21829,58 @@
     </row>
     <row r="8" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B8" s="5">
         <v>145.30000000000001</v>
       </c>
       <c r="C8" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>481</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B9" s="5">
         <v>30</v>
       </c>
       <c r="C9" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>484</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B10" s="5">
         <v>19.75</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B11" s="5">
         <v>36</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -21893,63 +21893,63 @@
     </row>
     <row r="13" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>224</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B14" s="5">
         <v>124</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B15" s="5">
         <v>1</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B16" s="5">
         <v>818.4</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B17" s="5">
         <v>318</v>
@@ -21961,35 +21961,35 @@
     </row>
     <row r="18" spans="1:4" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B18" s="5">
         <v>570</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B19" s="5">
         <v>1.9E-2</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="155" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B20" s="156"/>
       <c r="C20" s="156"/>
@@ -21997,77 +21997,77 @@
     </row>
     <row r="21" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B21" s="5">
         <v>4</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B22" s="5">
         <v>1</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B23" s="5">
         <v>124</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B24" s="5">
         <v>1</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B25" s="5">
         <v>880.8</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B26" s="5">
         <v>309</v>
@@ -22076,26 +22076,26 @@
         <v>188</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B27" s="5">
         <v>49.2</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B28" s="5">
         <v>14</v>
@@ -22104,12 +22104,12 @@
         <v>188</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B29" s="5">
         <v>14</v>
@@ -22118,12 +22118,12 @@
         <v>188</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="155" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B30" s="156"/>
       <c r="C30" s="156"/>
@@ -22131,69 +22131,69 @@
     </row>
     <row r="31" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="20" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B31" s="5">
         <v>5</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="20" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B32" s="5">
         <v>2</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B33" s="5">
         <v>9</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="20" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B34" s="5">
         <v>213</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="27" customFormat="1" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B35" s="24">
         <v>48</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="27" customFormat="1" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B36" s="24">
         <v>277</v>
@@ -22203,7 +22203,7 @@
     </row>
     <row r="37" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="155" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B37" s="156"/>
       <c r="C37" s="156"/>
@@ -22211,7 +22211,7 @@
     </row>
     <row r="38" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B38" s="5">
         <v>54.2</v>
@@ -22220,12 +22220,12 @@
         <v>188</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B39" s="5">
         <v>56.3</v>
@@ -22234,12 +22234,12 @@
         <v>188</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B40" s="5">
         <v>39.700000000000003</v>
@@ -22248,12 +22248,12 @@
         <v>188</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B41" s="5">
         <v>95.3</v>
@@ -22262,12 +22262,12 @@
         <v>188</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B42" s="5">
         <v>2571.9</v>
@@ -22276,12 +22276,12 @@
         <v>188</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B43" s="5">
         <v>925.3</v>
@@ -22290,12 +22290,12 @@
         <v>188</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="155" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B44" s="156"/>
       <c r="C44" s="156"/>
@@ -22303,21 +22303,21 @@
     </row>
     <row r="45" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B45" s="5">
         <v>8.3000000000000007</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="155" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B46" s="156"/>
       <c r="C46" s="156"/>
@@ -22325,7 +22325,7 @@
     </row>
     <row r="47" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B47" s="5">
         <v>156</v>
@@ -22334,40 +22334,40 @@
         <v>188</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B48" s="5">
         <v>4</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B49" s="5">
         <v>0.86</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="155" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B50" s="156"/>
       <c r="C50" s="156"/>
@@ -22375,30 +22375,30 @@
     </row>
     <row r="51" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B51" s="5">
         <v>1.1100000000000001</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B52" s="5">
         <v>1.587</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -22430,7 +22430,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>39</v>
@@ -23687,16 +23687,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>468</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>469</v>
-      </c>
-      <c r="C1" s="34" t="s">
+      <c r="D1" s="34" t="s">
         <v>550</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>551</v>
       </c>
       <c r="E1" s="34" t="s">
         <v>21</v>
@@ -23704,7 +23704,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B2" s="2">
         <v>6.5389932052543287E-2</v>
@@ -23712,7 +23712,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -23720,7 +23720,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -23728,7 +23728,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -23736,7 +23736,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B6">
         <v>1800</v>
@@ -23744,7 +23744,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -23752,7 +23752,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B8">
         <v>0.03</v>
@@ -23766,13 +23766,13 @@
         <v>0.08</v>
       </c>
       <c r="C9" s="158" t="s">
+        <v>558</v>
+      </c>
+      <c r="D9" s="158" t="s">
         <v>559</v>
       </c>
-      <c r="D9" s="158" t="s">
+      <c r="E9" s="158" t="s">
         <v>560</v>
-      </c>
-      <c r="E9" s="158" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -23861,10 +23861,10 @@
       </c>
       <c r="C17" s="159"/>
       <c r="D17" t="s">
+        <v>561</v>
+      </c>
+      <c r="E17" t="s">
         <v>562</v>
-      </c>
-      <c r="E17" t="s">
-        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -23931,10 +23931,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="91" t="s">
+        <v>563</v>
+      </c>
+      <c r="G1" s="92" t="s">
         <v>564</v>
-      </c>
-      <c r="G1" s="92" t="s">
-        <v>565</v>
       </c>
       <c r="H1" s="91" t="s">
         <v>5</v>
@@ -24093,7 +24093,7 @@
         <v>35</v>
       </c>
       <c r="F3" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G3" s="97">
         <v>1</v>
@@ -24127,7 +24127,7 @@
       <c r="T3" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="164" t="s">
+      <c r="U3" s="163" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="108"/>
@@ -24195,7 +24195,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G4" s="97">
         <v>1</v>
@@ -24294,7 +24294,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G5" s="97">
         <v>1</v>
@@ -24323,7 +24323,7 @@
       <c r="T5" s="160" t="s">
         <v>63</v>
       </c>
-      <c r="U5" s="164" t="s">
+      <c r="U5" s="163" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="108"/>
@@ -24391,7 +24391,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G6" s="97">
         <v>1</v>
@@ -24483,7 +24483,7 @@
         <v>35</v>
       </c>
       <c r="F7" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G7" s="97">
         <v>1</v>
@@ -24738,7 +24738,7 @@
         <v>35</v>
       </c>
       <c r="F11" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G11" s="97">
         <v>1</v>
@@ -24773,7 +24773,7 @@
       <c r="T11" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="163" t="s">
+      <c r="U11" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="108"/>
@@ -24841,7 +24841,7 @@
         <v>35</v>
       </c>
       <c r="F12" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G12" s="97">
         <v>1</v>
@@ -24938,7 +24938,7 @@
         <v>35</v>
       </c>
       <c r="F13" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G13" s="97">
         <v>1</v>
@@ -25018,7 +25018,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="101" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D14" s="96" t="str">
         <f t="shared" si="0"/>
@@ -25028,7 +25028,7 @@
         <v>35</v>
       </c>
       <c r="F14" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G14" s="97">
         <v>1</v>
@@ -25095,7 +25095,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="101" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D15" s="96" t="str">
         <f t="shared" si="0"/>
@@ -25105,7 +25105,7 @@
         <v>35</v>
       </c>
       <c r="F15" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G15" s="97">
         <v>1</v>
@@ -25118,10 +25118,10 @@
         <v>246.06299212598424</v>
       </c>
       <c r="L15" s="103" t="s">
+        <v>568</v>
+      </c>
+      <c r="M15" s="103" t="s">
         <v>569</v>
-      </c>
-      <c r="M15" s="103" t="s">
-        <v>570</v>
       </c>
       <c r="N15" s="104"/>
       <c r="O15" s="103"/>
@@ -25133,13 +25133,13 @@
         <v>73</v>
       </c>
       <c r="S15" s="106" t="s">
+        <v>570</v>
+      </c>
+      <c r="T15" s="106" t="s">
         <v>571</v>
       </c>
-      <c r="T15" s="106" t="s">
+      <c r="U15" s="116" t="s">
         <v>572</v>
-      </c>
-      <c r="U15" s="116" t="s">
-        <v>573</v>
       </c>
       <c r="V15" s="108"/>
       <c r="W15" s="99" t="s">
@@ -25189,7 +25189,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="101" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D16" s="96" t="str">
         <f t="shared" si="0"/>
@@ -25234,7 +25234,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="101" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D17" s="96" t="str">
         <f t="shared" si="0"/>
@@ -25290,7 +25290,7 @@
         <v>35</v>
       </c>
       <c r="F18" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G18" s="97">
         <v>1</v>
@@ -25321,12 +25321,12 @@
         <v>86</v>
       </c>
       <c r="S18" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T18" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U18" s="163" t="s">
+      <c r="U18" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V18" s="108"/>
@@ -25388,7 +25388,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G19" s="97">
         <v>1</v>
@@ -25480,7 +25480,7 @@
         <v>35</v>
       </c>
       <c r="F20" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G20" s="97">
         <v>1</v>
@@ -25561,7 +25561,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D21" s="96" t="str">
         <f t="shared" si="0"/>
@@ -25571,7 +25571,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G21" s="97">
         <v>1</v>
@@ -25645,7 +25645,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="101" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D22" s="96" t="str">
         <f t="shared" si="0"/>
@@ -25701,7 +25701,7 @@
         <v>35</v>
       </c>
       <c r="F23" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G23" s="97">
         <v>1</v>
@@ -25732,12 +25732,12 @@
         <v>86</v>
       </c>
       <c r="S23" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T23" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U23" s="163" t="s">
+      <c r="U23" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V23" s="108"/>
@@ -25799,7 +25799,7 @@
         <v>35</v>
       </c>
       <c r="F24" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G24" s="97">
         <v>1</v>
@@ -25891,7 +25891,7 @@
         <v>35</v>
       </c>
       <c r="F25" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G25" s="97">
         <v>1</v>
@@ -25972,7 +25972,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D26" s="96" t="str">
         <f t="shared" si="0"/>
@@ -25982,7 +25982,7 @@
         <v>35</v>
       </c>
       <c r="F26" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G26" s="97">
         <v>1</v>
@@ -26056,7 +26056,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="101" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D27" s="96" t="str">
         <f t="shared" si="0"/>
@@ -26112,7 +26112,7 @@
         <v>35</v>
       </c>
       <c r="F28" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G28" s="97">
         <v>1</v>
@@ -26143,12 +26143,12 @@
         <v>86</v>
       </c>
       <c r="S28" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T28" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U28" s="163" t="s">
+      <c r="U28" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V28" s="108"/>
@@ -26210,7 +26210,7 @@
         <v>35</v>
       </c>
       <c r="F29" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G29" s="97">
         <v>1</v>
@@ -26302,7 +26302,7 @@
         <v>35</v>
       </c>
       <c r="F30" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G30" s="97">
         <v>1</v>
@@ -26383,7 +26383,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D31" s="96" t="str">
         <f t="shared" si="0"/>
@@ -26393,7 +26393,7 @@
         <v>35</v>
       </c>
       <c r="F31" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G31" s="97">
         <v>1</v>
@@ -26467,7 +26467,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="101" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D32" s="96" t="str">
         <f t="shared" si="0"/>
@@ -26523,7 +26523,7 @@
         <v>35</v>
       </c>
       <c r="F33" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G33" s="97">
         <v>1</v>
@@ -26554,12 +26554,12 @@
         <v>86</v>
       </c>
       <c r="S33" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T33" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U33" s="163" t="s">
+      <c r="U33" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V33" s="108"/>
@@ -26621,7 +26621,7 @@
         <v>35</v>
       </c>
       <c r="F34" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G34" s="97">
         <v>1</v>
@@ -26713,7 +26713,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G35" s="97">
         <v>1</v>
@@ -26794,7 +26794,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D36" s="96" t="str">
         <f t="shared" si="2"/>
@@ -26804,7 +26804,7 @@
         <v>35</v>
       </c>
       <c r="F36" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G36" s="97">
         <v>1</v>
@@ -26878,7 +26878,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="101" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D37" s="96" t="str">
         <f t="shared" si="2"/>
@@ -26934,7 +26934,7 @@
         <v>35</v>
       </c>
       <c r="F38" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G38" s="97">
         <v>1</v>
@@ -26965,12 +26965,12 @@
         <v>86</v>
       </c>
       <c r="S38" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T38" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U38" s="163" t="s">
+      <c r="U38" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V38" s="108"/>
@@ -27032,7 +27032,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G39" s="97">
         <v>1</v>
@@ -27124,7 +27124,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G40" s="97">
         <v>1</v>
@@ -27205,7 +27205,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D41" s="96" t="str">
         <f t="shared" si="2"/>
@@ -27215,7 +27215,7 @@
         <v>35</v>
       </c>
       <c r="F41" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G41" s="97">
         <v>1</v>
@@ -27289,7 +27289,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="101" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D42" s="96" t="str">
         <f t="shared" si="2"/>
@@ -27299,7 +27299,7 @@
         <v>35</v>
       </c>
       <c r="F42" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G42" s="97">
         <v>1</v>
@@ -27312,10 +27312,10 @@
         <v>246.06299212598424</v>
       </c>
       <c r="L42" s="103" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M42" s="103" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="N42" s="104"/>
       <c r="O42" s="103"/>
@@ -27327,13 +27327,13 @@
         <v>73</v>
       </c>
       <c r="S42" s="106" t="s">
+        <v>570</v>
+      </c>
+      <c r="T42" s="106" t="s">
         <v>571</v>
       </c>
-      <c r="T42" s="106" t="s">
+      <c r="U42" s="116" t="s">
         <v>572</v>
-      </c>
-      <c r="U42" s="116" t="s">
-        <v>573</v>
       </c>
       <c r="V42" s="108"/>
       <c r="W42" s="99" t="s">
@@ -27383,7 +27383,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="101" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D43" s="96" t="str">
         <f t="shared" si="2"/>
@@ -27428,7 +27428,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="101" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D44" s="96" t="str">
         <f t="shared" si="2"/>
@@ -27484,7 +27484,7 @@
         <v>35</v>
       </c>
       <c r="F45" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G45" s="97">
         <v>1</v>
@@ -27515,12 +27515,12 @@
         <v>86</v>
       </c>
       <c r="S45" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T45" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U45" s="163" t="s">
+      <c r="U45" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V45" s="108"/>
@@ -27582,7 +27582,7 @@
         <v>35</v>
       </c>
       <c r="F46" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G46" s="97">
         <v>1</v>
@@ -27674,7 +27674,7 @@
         <v>35</v>
       </c>
       <c r="F47" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G47" s="97">
         <v>1</v>
@@ -27755,7 +27755,7 @@
         <v>4</v>
       </c>
       <c r="C48" s="101" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D48" s="96" t="str">
         <f t="shared" si="2"/>
@@ -27765,7 +27765,7 @@
         <v>35</v>
       </c>
       <c r="F48" s="96" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G48" s="97"/>
       <c r="H48" s="96"/>
@@ -27830,7 +27830,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="101" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D49" s="96" t="str">
         <f t="shared" si="2"/>
@@ -27840,7 +27840,7 @@
         <v>35</v>
       </c>
       <c r="F49" s="96" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G49" s="97">
         <v>4</v>
@@ -27907,7 +27907,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D50" s="96" t="str">
         <f t="shared" si="2"/>
@@ -27917,7 +27917,7 @@
         <v>35</v>
       </c>
       <c r="F50" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G50" s="97">
         <v>1</v>
@@ -27989,7 +27989,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="101" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D51" s="96"/>
       <c r="E51" s="96"/>
@@ -28042,7 +28042,7 @@
         <v>35</v>
       </c>
       <c r="F52" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G52" s="97">
         <v>1</v>
@@ -28073,12 +28073,12 @@
         <v>86</v>
       </c>
       <c r="S52" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T52" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="163" t="s">
+      <c r="U52" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V52" s="108"/>
@@ -28140,7 +28140,7 @@
         <v>35</v>
       </c>
       <c r="F53" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G53" s="97">
         <v>1</v>
@@ -28232,7 +28232,7 @@
         <v>35</v>
       </c>
       <c r="F54" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G54" s="97">
         <v>1</v>
@@ -28313,7 +28313,7 @@
         <v>4</v>
       </c>
       <c r="C55" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D55" s="96" t="str">
         <f t="shared" si="3"/>
@@ -28323,7 +28323,7 @@
         <v>35</v>
       </c>
       <c r="F55" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G55" s="97">
         <v>1</v>
@@ -28402,7 +28402,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="101" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D56" s="96" t="str">
         <f t="shared" si="3"/>
@@ -28458,7 +28458,7 @@
         <v>35</v>
       </c>
       <c r="F57" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G57" s="97">
         <v>1</v>
@@ -28489,12 +28489,12 @@
         <v>86</v>
       </c>
       <c r="S57" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T57" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="163" t="s">
+      <c r="U57" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="108"/>
@@ -28556,7 +28556,7 @@
         <v>35</v>
       </c>
       <c r="F58" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G58" s="97">
         <v>1</v>
@@ -28648,7 +28648,7 @@
         <v>35</v>
       </c>
       <c r="F59" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G59" s="97">
         <v>1</v>
@@ -28729,7 +28729,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D60" s="96" t="str">
         <f t="shared" si="3"/>
@@ -28739,7 +28739,7 @@
         <v>35</v>
       </c>
       <c r="F60" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G60" s="97">
         <v>1</v>
@@ -28813,7 +28813,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="101" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D61" s="96" t="str">
         <f t="shared" si="3"/>
@@ -28876,7 +28876,7 @@
         <v>35</v>
       </c>
       <c r="F62" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G62" s="97">
         <v>1</v>
@@ -28907,12 +28907,12 @@
         <v>86</v>
       </c>
       <c r="S62" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T62" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U62" s="163" t="s">
+      <c r="U62" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V62" s="108"/>
@@ -28974,7 +28974,7 @@
         <v>35</v>
       </c>
       <c r="F63" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G63" s="97">
         <v>1</v>
@@ -29066,7 +29066,7 @@
         <v>35</v>
       </c>
       <c r="F64" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G64" s="97">
         <v>1</v>
@@ -29147,7 +29147,7 @@
         <v>4</v>
       </c>
       <c r="C65" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D65" s="96" t="str">
         <f t="shared" si="3"/>
@@ -29157,7 +29157,7 @@
         <v>35</v>
       </c>
       <c r="F65" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G65" s="97">
         <v>1</v>
@@ -29231,7 +29231,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="101" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D66" s="96" t="str">
         <f t="shared" si="3"/>
@@ -29287,7 +29287,7 @@
         <v>35</v>
       </c>
       <c r="F67" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G67" s="97">
         <v>1</v>
@@ -29318,12 +29318,12 @@
         <v>86</v>
       </c>
       <c r="S67" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T67" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U67" s="163" t="s">
+      <c r="U67" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V67" s="108"/>
@@ -29385,7 +29385,7 @@
         <v>35</v>
       </c>
       <c r="F68" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G68" s="97">
         <v>1</v>
@@ -29477,7 +29477,7 @@
         <v>35</v>
       </c>
       <c r="F69" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G69" s="97">
         <v>1</v>
@@ -29558,7 +29558,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D70" s="96" t="str">
         <f t="shared" si="3"/>
@@ -29568,7 +29568,7 @@
         <v>35</v>
       </c>
       <c r="F70" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G70" s="97">
         <v>1</v>
@@ -29642,7 +29642,7 @@
         <v>3</v>
       </c>
       <c r="C71" s="101" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D71" s="96" t="str">
         <f t="shared" si="3"/>
@@ -29652,7 +29652,7 @@
         <v>35</v>
       </c>
       <c r="F71" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G71" s="97">
         <v>1</v>
@@ -29665,10 +29665,10 @@
         <v>246.06299212598424</v>
       </c>
       <c r="L71" s="103" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M71" s="103" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="N71" s="104"/>
       <c r="O71" s="103"/>
@@ -29680,13 +29680,13 @@
         <v>73</v>
       </c>
       <c r="S71" s="106" t="s">
+        <v>570</v>
+      </c>
+      <c r="T71" s="106" t="s">
         <v>571</v>
       </c>
-      <c r="T71" s="106" t="s">
+      <c r="U71" s="116" t="s">
         <v>572</v>
-      </c>
-      <c r="U71" s="116" t="s">
-        <v>573</v>
       </c>
       <c r="V71" s="108"/>
       <c r="W71" s="99" t="s">
@@ -29736,7 +29736,7 @@
         <v>2</v>
       </c>
       <c r="C72" s="101" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D72" s="96" t="str">
         <f t="shared" si="3"/>
@@ -29781,7 +29781,7 @@
         <v>3</v>
       </c>
       <c r="C73" s="101" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D73" s="96" t="str">
         <f t="shared" si="3"/>
@@ -29837,7 +29837,7 @@
         <v>35</v>
       </c>
       <c r="F74" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G74" s="97">
         <v>1</v>
@@ -29873,7 +29873,7 @@
       <c r="T74" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U74" s="163" t="s">
+      <c r="U74" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V74" s="108"/>
@@ -29935,7 +29935,7 @@
         <v>35</v>
       </c>
       <c r="F75" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G75" s="97">
         <v>1</v>
@@ -30027,7 +30027,7 @@
         <v>35</v>
       </c>
       <c r="F76" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G76" s="97">
         <v>1</v>
@@ -30108,7 +30108,7 @@
         <v>4</v>
       </c>
       <c r="C77" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D77" s="96" t="str">
         <f t="shared" si="3"/>
@@ -30118,7 +30118,7 @@
         <v>35</v>
       </c>
       <c r="F77" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G77" s="97">
         <v>1</v>
@@ -30192,7 +30192,7 @@
         <v>3</v>
       </c>
       <c r="C78" s="101" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D78" s="96" t="str">
         <f t="shared" si="3"/>
@@ -30248,7 +30248,7 @@
         <v>35</v>
       </c>
       <c r="F79" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G79" s="97">
         <v>1</v>
@@ -30284,7 +30284,7 @@
       <c r="T79" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U79" s="163" t="s">
+      <c r="U79" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V79" s="108"/>
@@ -30346,7 +30346,7 @@
         <v>35</v>
       </c>
       <c r="F80" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G80" s="97">
         <v>1</v>
@@ -30438,7 +30438,7 @@
         <v>35</v>
       </c>
       <c r="F81" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G81" s="97">
         <v>1</v>
@@ -30519,7 +30519,7 @@
         <v>4</v>
       </c>
       <c r="C82" s="101" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D82" s="96" t="str">
         <f t="shared" si="3"/>
@@ -30529,7 +30529,7 @@
         <v>35</v>
       </c>
       <c r="F82" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G82" s="97"/>
       <c r="H82" s="96"/>
@@ -30594,7 +30594,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="101" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D83" s="96" t="str">
         <f t="shared" si="3"/>
@@ -30604,7 +30604,7 @@
         <v>35</v>
       </c>
       <c r="F83" s="96" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G83" s="97">
         <v>4</v>
@@ -30671,7 +30671,7 @@
         <v>4</v>
       </c>
       <c r="C84" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D84" s="96" t="str">
         <f t="shared" si="3"/>
@@ -30681,7 +30681,7 @@
         <v>35</v>
       </c>
       <c r="F84" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G84" s="97">
         <v>1</v>
@@ -30755,7 +30755,7 @@
         <v>3</v>
       </c>
       <c r="C85" s="101" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D85" s="96" t="str">
         <f>REPT("   ", B85*2) &amp; C85</f>
@@ -30811,7 +30811,7 @@
         <v>35</v>
       </c>
       <c r="F86" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G86" s="97">
         <v>1</v>
@@ -30847,7 +30847,7 @@
       <c r="T86" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U86" s="163" t="s">
+      <c r="U86" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V86" s="108"/>
@@ -30909,7 +30909,7 @@
         <v>35</v>
       </c>
       <c r="F87" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G87" s="97">
         <v>1</v>
@@ -31001,7 +31001,7 @@
         <v>35</v>
       </c>
       <c r="F88" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G88" s="97">
         <v>1</v>
@@ -31082,7 +31082,7 @@
         <v>4</v>
       </c>
       <c r="C89" s="101" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D89" s="96" t="str">
         <f t="shared" si="3"/>
@@ -31092,7 +31092,7 @@
         <v>35</v>
       </c>
       <c r="F89" s="96" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G89" s="97"/>
       <c r="H89" s="96"/>
@@ -31157,7 +31157,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="101" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D90" s="96" t="str">
         <f t="shared" si="3"/>
@@ -31167,7 +31167,7 @@
         <v>35</v>
       </c>
       <c r="F90" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G90" s="97">
         <v>4</v>
@@ -31234,7 +31234,7 @@
         <v>4</v>
       </c>
       <c r="C91" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D91" s="96" t="str">
         <f t="shared" si="3"/>
@@ -31244,7 +31244,7 @@
         <v>35</v>
       </c>
       <c r="F91" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G91" s="97">
         <v>1</v>
@@ -31314,7 +31314,7 @@
         <v>3</v>
       </c>
       <c r="C92" s="101" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D92" s="96" t="str">
         <f t="shared" si="3"/>
@@ -31370,7 +31370,7 @@
         <v>35</v>
       </c>
       <c r="F93" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G93" s="97">
         <v>1</v>
@@ -31401,12 +31401,12 @@
         <v>86</v>
       </c>
       <c r="S93" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T93" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U93" s="163" t="s">
+      <c r="U93" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V93" s="108"/>
@@ -31468,7 +31468,7 @@
         <v>35</v>
       </c>
       <c r="F94" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G94" s="97">
         <v>1</v>
@@ -31560,7 +31560,7 @@
         <v>35</v>
       </c>
       <c r="F95" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G95" s="97">
         <v>1</v>
@@ -31641,7 +31641,7 @@
         <v>4</v>
       </c>
       <c r="C96" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D96" s="96" t="str">
         <f t="shared" si="3"/>
@@ -31651,7 +31651,7 @@
         <v>35</v>
       </c>
       <c r="F96" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G96" s="97">
         <v>1</v>
@@ -31725,7 +31725,7 @@
         <v>3</v>
       </c>
       <c r="C97" s="101" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D97" s="96" t="str">
         <f t="shared" si="3"/>
@@ -31781,7 +31781,7 @@
         <v>35</v>
       </c>
       <c r="F98" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G98" s="97">
         <v>1</v>
@@ -31812,12 +31812,12 @@
         <v>86</v>
       </c>
       <c r="S98" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T98" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U98" s="163" t="s">
+      <c r="U98" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V98" s="108"/>
@@ -31879,7 +31879,7 @@
         <v>35</v>
       </c>
       <c r="F99" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G99" s="97">
         <v>1</v>
@@ -31971,7 +31971,7 @@
         <v>35</v>
       </c>
       <c r="F100" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G100" s="97">
         <v>1</v>
@@ -32052,7 +32052,7 @@
         <v>4</v>
       </c>
       <c r="C101" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D101" s="96" t="str">
         <f t="shared" si="3"/>
@@ -32062,7 +32062,7 @@
         <v>35</v>
       </c>
       <c r="F101" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G101" s="97">
         <v>1</v>
@@ -32136,7 +32136,7 @@
         <v>3</v>
       </c>
       <c r="C102" s="101" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D102" s="96" t="str">
         <f t="shared" si="3"/>
@@ -32146,7 +32146,7 @@
         <v>35</v>
       </c>
       <c r="F102" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G102" s="97">
         <v>1</v>
@@ -32159,10 +32159,10 @@
         <v>246.06299212598424</v>
       </c>
       <c r="L102" s="103" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M102" s="103" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N102" s="104"/>
       <c r="O102" s="103"/>
@@ -32174,13 +32174,13 @@
         <v>73</v>
       </c>
       <c r="S102" s="106" t="s">
+        <v>570</v>
+      </c>
+      <c r="T102" s="106" t="s">
         <v>571</v>
       </c>
-      <c r="T102" s="106" t="s">
+      <c r="U102" s="116" t="s">
         <v>572</v>
-      </c>
-      <c r="U102" s="116" t="s">
-        <v>573</v>
       </c>
       <c r="V102" s="108"/>
       <c r="W102" s="99" t="s">
@@ -32237,7 +32237,7 @@
         <v>2</v>
       </c>
       <c r="C103" s="101" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D103" s="96" t="str">
         <f t="shared" si="3"/>
@@ -32289,7 +32289,7 @@
         <v>3</v>
       </c>
       <c r="C104" s="101" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D104" s="96" t="str">
         <f t="shared" si="3"/>
@@ -32352,7 +32352,7 @@
         <v>35</v>
       </c>
       <c r="F105" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G105" s="97">
         <v>1</v>
@@ -32383,12 +32383,12 @@
         <v>86</v>
       </c>
       <c r="S105" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T105" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U105" s="163" t="s">
+      <c r="U105" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V105" s="108"/>
@@ -32457,7 +32457,7 @@
         <v>35</v>
       </c>
       <c r="F106" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G106" s="97">
         <v>1</v>
@@ -32549,7 +32549,7 @@
         <v>35</v>
       </c>
       <c r="F107" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G107" s="97">
         <v>1</v>
@@ -32630,7 +32630,7 @@
         <v>4</v>
       </c>
       <c r="C108" s="101" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D108" s="96" t="str">
         <f t="shared" si="3"/>
@@ -32640,7 +32640,7 @@
         <v>35</v>
       </c>
       <c r="F108" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G108" s="97">
         <v>1</v>
@@ -32707,7 +32707,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="101" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D109" s="96" t="str">
         <f t="shared" si="3"/>
@@ -32717,7 +32717,7 @@
         <v>35</v>
       </c>
       <c r="F109" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G109" s="97">
         <v>1</v>
@@ -32784,7 +32784,7 @@
         <v>4</v>
       </c>
       <c r="C110" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D110" s="96" t="str">
         <f t="shared" si="3"/>
@@ -32794,7 +32794,7 @@
         <v>35</v>
       </c>
       <c r="F110" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G110" s="97">
         <v>1</v>
@@ -32807,7 +32807,7 @@
         <v>80</v>
       </c>
       <c r="M110" s="101" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="N110" s="104"/>
       <c r="O110" s="103" t="s">
@@ -32867,7 +32867,7 @@
         <v>3</v>
       </c>
       <c r="C111" s="101" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D111" s="96" t="str">
         <f t="shared" si="3"/>
@@ -32923,7 +32923,7 @@
         <v>35</v>
       </c>
       <c r="F112" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G112" s="97">
         <v>1</v>
@@ -32959,7 +32959,7 @@
       <c r="T112" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U112" s="163" t="s">
+      <c r="U112" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V112" s="108"/>
@@ -33021,7 +33021,7 @@
         <v>35</v>
       </c>
       <c r="F113" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G113" s="97">
         <v>1</v>
@@ -33113,7 +33113,7 @@
         <v>35</v>
       </c>
       <c r="F114" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G114" s="97">
         <v>1</v>
@@ -33194,7 +33194,7 @@
         <v>4</v>
       </c>
       <c r="C115" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D115" s="96" t="str">
         <f t="shared" si="3"/>
@@ -33204,7 +33204,7 @@
         <v>35</v>
       </c>
       <c r="F115" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G115" s="97">
         <v>1</v>
@@ -33217,7 +33217,7 @@
         <v>80</v>
       </c>
       <c r="M115" s="101" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="N115" s="104"/>
       <c r="O115" s="103" t="s">
@@ -33284,7 +33284,7 @@
         <v>3</v>
       </c>
       <c r="C116" s="101" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D116" s="96" t="str">
         <f t="shared" ref="D116:D179" si="7">REPT("   ", B116*2) &amp; C116</f>
@@ -33347,7 +33347,7 @@
         <v>35</v>
       </c>
       <c r="F117" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G117" s="97">
         <v>1</v>
@@ -33378,12 +33378,12 @@
         <v>86</v>
       </c>
       <c r="S117" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T117" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U117" s="163" t="s">
+      <c r="U117" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V117" s="108"/>
@@ -33452,7 +33452,7 @@
         <v>35</v>
       </c>
       <c r="F118" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G118" s="97">
         <v>1</v>
@@ -33551,7 +33551,7 @@
         <v>35</v>
       </c>
       <c r="F119" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G119" s="97">
         <v>1</v>
@@ -33639,7 +33639,7 @@
         <v>4</v>
       </c>
       <c r="C120" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D120" s="96" t="str">
         <f t="shared" si="7"/>
@@ -33649,7 +33649,7 @@
         <v>35</v>
       </c>
       <c r="F120" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G120" s="97">
         <v>1</v>
@@ -33730,7 +33730,7 @@
         <v>3</v>
       </c>
       <c r="C121" s="101" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D121" s="96" t="str">
         <f t="shared" si="7"/>
@@ -33786,7 +33786,7 @@
         <v>35</v>
       </c>
       <c r="F122" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G122" s="97">
         <v>1</v>
@@ -33817,12 +33817,12 @@
         <v>86</v>
       </c>
       <c r="S122" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T122" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U122" s="163" t="s">
+      <c r="U122" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V122" s="108"/>
@@ -33884,7 +33884,7 @@
         <v>35</v>
       </c>
       <c r="F123" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G123" s="97">
         <v>1</v>
@@ -33976,7 +33976,7 @@
         <v>35</v>
       </c>
       <c r="F124" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G124" s="97">
         <v>1</v>
@@ -34057,7 +34057,7 @@
         <v>4</v>
       </c>
       <c r="C125" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D125" s="96" t="str">
         <f t="shared" si="7"/>
@@ -34067,7 +34067,7 @@
         <v>35</v>
       </c>
       <c r="F125" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G125" s="97">
         <v>1</v>
@@ -34141,7 +34141,7 @@
         <v>3</v>
       </c>
       <c r="C126" s="101" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D126" s="96" t="str">
         <f t="shared" si="7"/>
@@ -34197,7 +34197,7 @@
         <v>35</v>
       </c>
       <c r="F127" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G127" s="97">
         <v>1</v>
@@ -34228,12 +34228,12 @@
         <v>86</v>
       </c>
       <c r="S127" s="160" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T127" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U127" s="163" t="s">
+      <c r="U127" s="162" t="s">
         <v>76</v>
       </c>
       <c r="V127" s="108"/>
@@ -34295,7 +34295,7 @@
         <v>35</v>
       </c>
       <c r="F128" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G128" s="97">
         <v>1</v>
@@ -34387,7 +34387,7 @@
         <v>35</v>
       </c>
       <c r="F129" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G129" s="97">
         <v>1</v>
@@ -34468,7 +34468,7 @@
         <v>4</v>
       </c>
       <c r="C130" s="101" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D130" s="96" t="str">
         <f t="shared" si="7"/>
@@ -34478,7 +34478,7 @@
         <v>35</v>
       </c>
       <c r="F130" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G130" s="97">
         <v>1</v>
@@ -34552,7 +34552,7 @@
         <v>3</v>
       </c>
       <c r="C131" s="101" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D131" s="96" t="str">
         <f t="shared" si="7"/>
@@ -34562,7 +34562,7 @@
         <v>35</v>
       </c>
       <c r="F131" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G131" s="97">
         <v>1</v>
@@ -34575,10 +34575,10 @@
         <v>246.06299212598424</v>
       </c>
       <c r="L131" s="103" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M131" s="101" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="N131" s="104"/>
       <c r="O131" s="103"/>
@@ -34590,13 +34590,13 @@
         <v>73</v>
       </c>
       <c r="S131" s="106" t="s">
+        <v>570</v>
+      </c>
+      <c r="T131" s="106" t="s">
         <v>571</v>
       </c>
-      <c r="T131" s="106" t="s">
+      <c r="U131" s="116" t="s">
         <v>572</v>
-      </c>
-      <c r="U131" s="116" t="s">
-        <v>573</v>
       </c>
       <c r="V131" s="108"/>
       <c r="W131" s="99" t="s">
@@ -34646,7 +34646,7 @@
         <v>1</v>
       </c>
       <c r="C132" s="129" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D132" s="130" t="str">
         <f t="shared" si="7"/>
@@ -34656,7 +34656,7 @@
         <v>35</v>
       </c>
       <c r="F132" s="130" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G132" s="131">
         <v>1</v>
@@ -34668,16 +34668,16 @@
         <v>74748072.817566499</v>
       </c>
       <c r="L132" s="133" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M132" s="130" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="N132" s="134">
         <v>1</v>
       </c>
       <c r="O132" s="134" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="P132" s="135">
         <v>-0.97870000000000001</v>
@@ -34689,7 +34689,7 @@
         <v>86</v>
       </c>
       <c r="S132" s="136" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="T132" s="134"/>
       <c r="U132" s="134"/>
@@ -34739,7 +34739,7 @@
         <v>1</v>
       </c>
       <c r="C133" s="117" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D133" s="96" t="str">
         <f t="shared" si="7"/>
@@ -34784,7 +34784,7 @@
         <v>2</v>
       </c>
       <c r="C134" s="117" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D134" s="96" t="str">
         <f t="shared" si="7"/>
@@ -34829,7 +34829,7 @@
         <v>3</v>
       </c>
       <c r="C135" s="117" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D135" s="96" t="str">
         <f t="shared" si="7"/>
@@ -34839,7 +34839,7 @@
         <v>35</v>
       </c>
       <c r="F135" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G135" s="97">
         <v>12</v>
@@ -34862,12 +34862,12 @@
         <v>86</v>
       </c>
       <c r="S135" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T135" s="108"/>
       <c r="U135" s="108"/>
       <c r="V135" s="108" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="W135" s="99" t="s">
         <v>43</v>
@@ -34914,7 +34914,7 @@
         <v>3</v>
       </c>
       <c r="C136" s="117" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D136" s="96" t="str">
         <f t="shared" si="7"/>
@@ -34924,7 +34924,7 @@
         <v>35</v>
       </c>
       <c r="F136" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G136" s="97">
         <v>2</v>
@@ -34947,12 +34947,12 @@
         <v>86</v>
       </c>
       <c r="S136" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T136" s="108"/>
       <c r="U136" s="108"/>
       <c r="V136" s="108" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="W136" s="99" t="s">
         <v>43</v>
@@ -34999,7 +34999,7 @@
         <v>3</v>
       </c>
       <c r="C137" s="117" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D137" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35009,7 +35009,7 @@
         <v>35</v>
       </c>
       <c r="F137" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G137" s="97">
         <v>1</v>
@@ -35032,12 +35032,12 @@
         <v>86</v>
       </c>
       <c r="S137" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T137" s="108"/>
       <c r="U137" s="108"/>
       <c r="V137" s="108" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="W137" s="99" t="s">
         <v>43</v>
@@ -35084,7 +35084,7 @@
         <v>3</v>
       </c>
       <c r="C138" s="117" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D138" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35094,7 +35094,7 @@
         <v>35</v>
       </c>
       <c r="F138" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G138" s="97">
         <v>2</v>
@@ -35161,7 +35161,7 @@
         <v>3</v>
       </c>
       <c r="C139" s="117" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D139" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35171,7 +35171,7 @@
         <v>35</v>
       </c>
       <c r="F139" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G139" s="97">
         <v>1</v>
@@ -35194,16 +35194,16 @@
         <v>86</v>
       </c>
       <c r="S139" s="118" t="s">
+        <v>627</v>
+      </c>
+      <c r="T139" s="118" t="s">
         <v>628</v>
       </c>
-      <c r="T139" s="118" t="s">
+      <c r="U139" s="119" t="s">
         <v>629</v>
       </c>
-      <c r="U139" s="119" t="s">
+      <c r="V139" s="108" t="s">
         <v>630</v>
-      </c>
-      <c r="V139" s="108" t="s">
-        <v>631</v>
       </c>
       <c r="W139" s="99" t="s">
         <v>43</v>
@@ -35250,7 +35250,7 @@
         <v>3</v>
       </c>
       <c r="C140" s="117" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D140" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35260,7 +35260,7 @@
         <v>35</v>
       </c>
       <c r="F140" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G140" s="97">
         <v>1</v>
@@ -35327,7 +35327,7 @@
         <v>3</v>
       </c>
       <c r="C141" s="117" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D141" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35337,7 +35337,7 @@
         <v>35</v>
       </c>
       <c r="F141" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G141" s="97">
         <v>1</v>
@@ -35404,7 +35404,7 @@
         <v>2</v>
       </c>
       <c r="C142" s="117" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D142" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35449,7 +35449,7 @@
         <v>3</v>
       </c>
       <c r="C143" s="117" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D143" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35459,7 +35459,7 @@
         <v>35</v>
       </c>
       <c r="F143" s="96" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G143" s="97">
         <v>6</v>
@@ -35482,12 +35482,12 @@
         <v>86</v>
       </c>
       <c r="S143" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T143" s="108"/>
       <c r="U143" s="108"/>
       <c r="V143" s="108" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="W143" s="99" t="s">
         <v>43</v>
@@ -35534,7 +35534,7 @@
         <v>3</v>
       </c>
       <c r="C144" s="117" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D144" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35544,7 +35544,7 @@
         <v>35</v>
       </c>
       <c r="F144" s="96" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G144" s="97">
         <v>1</v>
@@ -35611,7 +35611,7 @@
         <v>3</v>
       </c>
       <c r="C145" s="117" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D145" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35621,7 +35621,7 @@
         <v>35</v>
       </c>
       <c r="F145" s="96" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G145" s="97">
         <v>1</v>
@@ -35641,7 +35641,7 @@
       <c r="T145" s="108"/>
       <c r="U145" s="108"/>
       <c r="V145" s="108" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W145" s="99" t="s">
         <v>43</v>
@@ -35690,7 +35690,7 @@
         <v>3</v>
       </c>
       <c r="C146" s="117" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D146" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35700,7 +35700,7 @@
         <v>35</v>
       </c>
       <c r="F146" s="96" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G146" s="97">
         <v>1</v>
@@ -35767,7 +35767,7 @@
         <v>3</v>
       </c>
       <c r="C147" s="117" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D147" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35777,7 +35777,7 @@
         <v>35</v>
       </c>
       <c r="F147" s="96" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G147" s="97">
         <v>1</v>
@@ -35844,7 +35844,7 @@
         <v>2</v>
       </c>
       <c r="C148" s="117" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D148" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35889,7 +35889,7 @@
         <v>3</v>
       </c>
       <c r="C149" s="117" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D149" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35899,7 +35899,7 @@
         <v>35</v>
       </c>
       <c r="F149" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G149" s="97">
         <v>1</v>
@@ -35966,7 +35966,7 @@
         <v>3</v>
       </c>
       <c r="C150" s="117" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D150" s="96" t="str">
         <f t="shared" si="7"/>
@@ -35976,7 +35976,7 @@
         <v>35</v>
       </c>
       <c r="F150" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G150" s="97">
         <v>1</v>
@@ -35990,7 +35990,7 @@
       </c>
       <c r="L150" s="108"/>
       <c r="M150" s="118" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="N150" s="108">
         <v>3417</v>
@@ -36013,7 +36013,7 @@
       <c r="T150" s="108"/>
       <c r="U150" s="108"/>
       <c r="V150" s="108" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W150" s="99" t="s">
         <v>43</v>
@@ -36062,7 +36062,7 @@
         <v>3</v>
       </c>
       <c r="C151" s="117" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D151" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36107,7 +36107,7 @@
         <v>4</v>
       </c>
       <c r="C152" s="117" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D152" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36117,7 +36117,7 @@
         <v>35</v>
       </c>
       <c r="F152" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G152" s="97">
         <v>1</v>
@@ -36133,7 +36133,7 @@
         <v>98</v>
       </c>
       <c r="M152" s="118" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="N152" s="108">
         <v>3417</v>
@@ -36210,7 +36210,7 @@
         <v>4</v>
       </c>
       <c r="C153" s="117" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D153" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36220,7 +36220,7 @@
         <v>35</v>
       </c>
       <c r="F153" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G153" s="97">
         <v>1</v>
@@ -36236,7 +36236,7 @@
         <v>98</v>
       </c>
       <c r="M153" s="118" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="N153" s="108">
         <v>3417</v>
@@ -36306,7 +36306,7 @@
         <v>4</v>
       </c>
       <c r="C154" s="117" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D154" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36316,7 +36316,7 @@
         <v>35</v>
       </c>
       <c r="F154" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G154" s="97">
         <v>1</v>
@@ -36332,7 +36332,7 @@
         <v>98</v>
       </c>
       <c r="M154" s="118" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="N154" s="108">
         <v>3417</v>
@@ -36402,7 +36402,7 @@
         <v>3</v>
       </c>
       <c r="C155" s="117" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D155" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36412,7 +36412,7 @@
         <v>35</v>
       </c>
       <c r="F155" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G155" s="97">
         <v>1</v>
@@ -36428,7 +36428,7 @@
         <v>80</v>
       </c>
       <c r="M155" s="118" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N155" s="108">
         <v>201049.28</v>
@@ -36447,13 +36447,13 @@
       </c>
       <c r="S155" s="118"/>
       <c r="T155" s="108" t="s">
+        <v>649</v>
+      </c>
+      <c r="U155" s="119" t="s">
         <v>650</v>
       </c>
-      <c r="U155" s="119" t="s">
+      <c r="V155" s="108" t="s">
         <v>651</v>
-      </c>
-      <c r="V155" s="108" t="s">
-        <v>652</v>
       </c>
       <c r="W155" s="99" t="s">
         <v>43</v>
@@ -36502,7 +36502,7 @@
         <v>2</v>
       </c>
       <c r="C156" s="117" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D156" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36547,7 +36547,7 @@
         <v>3</v>
       </c>
       <c r="C157" s="117" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D157" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36557,7 +36557,7 @@
         <v>35</v>
       </c>
       <c r="F157" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G157" s="97">
         <v>1</v>
@@ -36624,7 +36624,7 @@
         <v>3</v>
       </c>
       <c r="C158" s="117" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D158" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36634,7 +36634,7 @@
         <v>35</v>
       </c>
       <c r="F158" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G158" s="97">
         <v>1</v>
@@ -36701,7 +36701,7 @@
         <v>3</v>
       </c>
       <c r="C159" s="117" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D159" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36711,7 +36711,7 @@
         <v>35</v>
       </c>
       <c r="F159" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G159" s="97">
         <v>1</v>
@@ -36778,7 +36778,7 @@
         <v>2</v>
       </c>
       <c r="C160" s="117" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D160" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36823,7 +36823,7 @@
         <v>3</v>
       </c>
       <c r="C161" s="117" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D161" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36833,7 +36833,7 @@
         <v>35</v>
       </c>
       <c r="F161" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G161" s="97">
         <v>1</v>
@@ -36900,7 +36900,7 @@
         <v>3</v>
       </c>
       <c r="C162" s="117" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D162" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36910,7 +36910,7 @@
         <v>35</v>
       </c>
       <c r="F162" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G162" s="97">
         <v>0.1</v>
@@ -36977,7 +36977,7 @@
         <v>3</v>
       </c>
       <c r="C163" s="117" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D163" s="96" t="str">
         <f t="shared" si="7"/>
@@ -36987,7 +36987,7 @@
         <v>35</v>
       </c>
       <c r="F163" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G163" s="97">
         <v>0.1</v>
@@ -37054,7 +37054,7 @@
         <v>2</v>
       </c>
       <c r="C164" s="117" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D164" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37099,7 +37099,7 @@
         <v>3</v>
       </c>
       <c r="C165" s="117" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D165" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37109,7 +37109,7 @@
         <v>35</v>
       </c>
       <c r="F165" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G165" s="97">
         <v>1</v>
@@ -37176,7 +37176,7 @@
         <v>3</v>
       </c>
       <c r="C166" s="117" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D166" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37186,7 +37186,7 @@
         <v>35</v>
       </c>
       <c r="F166" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G166" s="97">
         <v>1</v>
@@ -37253,7 +37253,7 @@
         <v>3</v>
       </c>
       <c r="C167" s="117" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D167" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37263,7 +37263,7 @@
         <v>35</v>
       </c>
       <c r="F167" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G167" s="97">
         <v>1</v>
@@ -37330,7 +37330,7 @@
         <v>3</v>
       </c>
       <c r="C168" s="117" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D168" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37340,7 +37340,7 @@
         <v>35</v>
       </c>
       <c r="F168" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G168" s="97">
         <v>1</v>
@@ -37407,7 +37407,7 @@
         <v>3</v>
       </c>
       <c r="C169" s="117" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D169" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37417,7 +37417,7 @@
         <v>35</v>
       </c>
       <c r="F169" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G169" s="97">
         <v>1</v>
@@ -37484,7 +37484,7 @@
         <v>3</v>
       </c>
       <c r="C170" s="117" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D170" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37494,7 +37494,7 @@
         <v>35</v>
       </c>
       <c r="F170" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G170" s="97">
         <v>1</v>
@@ -37561,7 +37561,7 @@
         <v>1</v>
       </c>
       <c r="C171" s="117" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D171" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37606,7 +37606,7 @@
         <v>2</v>
       </c>
       <c r="C172" s="117" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D172" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37651,7 +37651,7 @@
         <v>3</v>
       </c>
       <c r="C173" s="117" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D173" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37661,7 +37661,7 @@
         <v>35</v>
       </c>
       <c r="F173" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G173" s="97"/>
       <c r="H173" s="96"/>
@@ -37726,7 +37726,7 @@
         <v>3</v>
       </c>
       <c r="C174" s="117" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D174" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37736,7 +37736,7 @@
         <v>35</v>
       </c>
       <c r="F174" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G174" s="97">
         <v>6</v>
@@ -37759,12 +37759,12 @@
         <v>86</v>
       </c>
       <c r="S174" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T174" s="108"/>
       <c r="U174" s="108"/>
       <c r="V174" s="108" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="W174" s="99" t="s">
         <v>43</v>
@@ -37811,7 +37811,7 @@
         <v>3</v>
       </c>
       <c r="C175" s="117" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D175" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37821,7 +37821,7 @@
         <v>35</v>
       </c>
       <c r="F175" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G175" s="97">
         <v>2</v>
@@ -37844,12 +37844,12 @@
         <v>86</v>
       </c>
       <c r="S175" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T175" s="108"/>
       <c r="U175" s="108"/>
       <c r="V175" s="108" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="W175" s="99" t="s">
         <v>43</v>
@@ -37896,7 +37896,7 @@
         <v>3</v>
       </c>
       <c r="C176" s="117" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D176" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37906,7 +37906,7 @@
         <v>35</v>
       </c>
       <c r="F176" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G176" s="97">
         <v>1</v>
@@ -37929,12 +37929,12 @@
         <v>86</v>
       </c>
       <c r="S176" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T176" s="108"/>
       <c r="U176" s="108"/>
       <c r="V176" s="108" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="W176" s="99" t="s">
         <v>43</v>
@@ -37981,7 +37981,7 @@
         <v>3</v>
       </c>
       <c r="C177" s="117" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D177" s="96" t="str">
         <f t="shared" si="7"/>
@@ -37991,7 +37991,7 @@
         <v>35</v>
       </c>
       <c r="F177" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G177" s="97">
         <v>1</v>
@@ -38058,7 +38058,7 @@
         <v>3</v>
       </c>
       <c r="C178" s="117" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D178" s="96" t="str">
         <f t="shared" si="7"/>
@@ -38068,7 +38068,7 @@
         <v>35</v>
       </c>
       <c r="F178" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G178" s="97">
         <v>1</v>
@@ -38135,7 +38135,7 @@
         <v>2</v>
       </c>
       <c r="C179" s="117" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D179" s="96" t="str">
         <f t="shared" si="7"/>
@@ -38180,7 +38180,7 @@
         <v>3</v>
       </c>
       <c r="C180" s="117" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D180" s="96" t="str">
         <f t="shared" ref="D180:D243" si="14">REPT("   ", B180*2) &amp; C180</f>
@@ -38190,7 +38190,7 @@
         <v>35</v>
       </c>
       <c r="F180" s="96" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G180" s="97">
         <v>6</v>
@@ -38213,12 +38213,12 @@
         <v>86</v>
       </c>
       <c r="S180" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T180" s="108"/>
       <c r="U180" s="108"/>
       <c r="V180" s="108" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="W180" s="99" t="s">
         <v>43</v>
@@ -38265,7 +38265,7 @@
         <v>3</v>
       </c>
       <c r="C181" s="117" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D181" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38275,7 +38275,7 @@
         <v>35</v>
       </c>
       <c r="F181" s="96" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G181" s="97">
         <v>1</v>
@@ -38342,7 +38342,7 @@
         <v>3</v>
       </c>
       <c r="C182" s="117" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D182" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38352,7 +38352,7 @@
         <v>35</v>
       </c>
       <c r="F182" s="96" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G182" s="97">
         <v>1</v>
@@ -38372,7 +38372,7 @@
       <c r="T182" s="108"/>
       <c r="U182" s="108"/>
       <c r="V182" s="108" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W182" s="99" t="s">
         <v>43</v>
@@ -38421,7 +38421,7 @@
         <v>3</v>
       </c>
       <c r="C183" s="117" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D183" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38431,7 +38431,7 @@
         <v>35</v>
       </c>
       <c r="F183" s="96" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G183" s="97">
         <v>1</v>
@@ -38498,7 +38498,7 @@
         <v>3</v>
       </c>
       <c r="C184" s="117" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D184" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38508,7 +38508,7 @@
         <v>35</v>
       </c>
       <c r="F184" s="96" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G184" s="97">
         <v>1</v>
@@ -38582,7 +38582,7 @@
         <v>2</v>
       </c>
       <c r="C185" s="117" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D185" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38634,7 +38634,7 @@
         <v>3</v>
       </c>
       <c r="C186" s="117" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D186" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38644,7 +38644,7 @@
         <v>35</v>
       </c>
       <c r="F186" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G186" s="97">
         <v>0.25</v>
@@ -38718,7 +38718,7 @@
         <v>3</v>
       </c>
       <c r="C187" s="117" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D187" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38728,7 +38728,7 @@
         <v>35</v>
       </c>
       <c r="F187" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G187" s="97">
         <v>0.1</v>
@@ -38795,7 +38795,7 @@
         <v>3</v>
       </c>
       <c r="C188" s="117" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D188" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38805,7 +38805,7 @@
         <v>35</v>
       </c>
       <c r="F188" s="96" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G188" s="97">
         <v>0.25</v>
@@ -38872,7 +38872,7 @@
         <v>2</v>
       </c>
       <c r="C189" s="117" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D189" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38917,7 +38917,7 @@
         <v>3</v>
       </c>
       <c r="C190" s="117" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D190" s="96" t="str">
         <f t="shared" si="14"/>
@@ -38927,7 +38927,7 @@
         <v>35</v>
       </c>
       <c r="F190" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G190" s="97">
         <v>1</v>
@@ -38994,7 +38994,7 @@
         <v>3</v>
       </c>
       <c r="C191" s="117" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D191" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39004,7 +39004,7 @@
         <v>35</v>
       </c>
       <c r="F191" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G191" s="97">
         <v>1</v>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="L191" s="108"/>
       <c r="M191" s="118" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N191" s="108">
         <v>3417</v>
@@ -39041,7 +39041,7 @@
       <c r="T191" s="108"/>
       <c r="U191" s="108"/>
       <c r="V191" s="108" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W191" s="99" t="s">
         <v>43</v>
@@ -39090,7 +39090,7 @@
         <v>3</v>
       </c>
       <c r="C192" s="117" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D192" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39135,7 +39135,7 @@
         <v>4</v>
       </c>
       <c r="C193" s="117" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D193" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39145,7 +39145,7 @@
         <v>35</v>
       </c>
       <c r="F193" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G193" s="97">
         <v>1</v>
@@ -39161,7 +39161,7 @@
         <v>98</v>
       </c>
       <c r="M193" s="118" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N193" s="108">
         <v>3417</v>
@@ -39231,7 +39231,7 @@
         <v>4</v>
       </c>
       <c r="C194" s="117" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D194" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39241,7 +39241,7 @@
         <v>35</v>
       </c>
       <c r="F194" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G194" s="97">
         <v>1</v>
@@ -39257,7 +39257,7 @@
         <v>98</v>
       </c>
       <c r="M194" s="118" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N194" s="108">
         <v>3417</v>
@@ -39327,7 +39327,7 @@
         <v>4</v>
       </c>
       <c r="C195" s="117" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D195" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39337,7 +39337,7 @@
         <v>35</v>
       </c>
       <c r="F195" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G195" s="97">
         <v>1</v>
@@ -39353,7 +39353,7 @@
         <v>98</v>
       </c>
       <c r="M195" s="118" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N195" s="108">
         <v>3417</v>
@@ -39423,7 +39423,7 @@
         <v>3</v>
       </c>
       <c r="C196" s="117" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D196" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39433,7 +39433,7 @@
         <v>35</v>
       </c>
       <c r="F196" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G196" s="97">
         <v>1</v>
@@ -39449,7 +39449,7 @@
         <v>80</v>
       </c>
       <c r="M196" s="118" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N196" s="108">
         <v>201049.28</v>
@@ -39468,13 +39468,13 @@
       </c>
       <c r="S196" s="118"/>
       <c r="T196" s="108" t="s">
+        <v>649</v>
+      </c>
+      <c r="U196" s="119" t="s">
         <v>650</v>
       </c>
-      <c r="U196" s="119" t="s">
+      <c r="V196" s="108" t="s">
         <v>651</v>
-      </c>
-      <c r="V196" s="108" t="s">
-        <v>652</v>
       </c>
       <c r="W196" s="99" t="s">
         <v>43</v>
@@ -39523,7 +39523,7 @@
         <v>2</v>
       </c>
       <c r="C197" s="117" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D197" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39568,7 +39568,7 @@
         <v>3</v>
       </c>
       <c r="C198" s="117" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D198" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39578,7 +39578,7 @@
         <v>35</v>
       </c>
       <c r="F198" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G198" s="97">
         <v>1</v>
@@ -39645,7 +39645,7 @@
         <v>3</v>
       </c>
       <c r="C199" s="117" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D199" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39655,7 +39655,7 @@
         <v>35</v>
       </c>
       <c r="F199" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G199" s="97">
         <v>1</v>
@@ -39722,7 +39722,7 @@
         <v>3</v>
       </c>
       <c r="C200" s="117" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D200" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39732,7 +39732,7 @@
         <v>35</v>
       </c>
       <c r="F200" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G200" s="97">
         <v>1</v>
@@ -39799,7 +39799,7 @@
         <v>3</v>
       </c>
       <c r="C201" s="117" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D201" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39809,7 +39809,7 @@
         <v>35</v>
       </c>
       <c r="F201" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G201" s="97">
         <v>1</v>
@@ -39876,7 +39876,7 @@
         <v>3</v>
       </c>
       <c r="C202" s="117" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D202" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39886,7 +39886,7 @@
         <v>35</v>
       </c>
       <c r="F202" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G202" s="97">
         <v>1</v>
@@ -39953,7 +39953,7 @@
         <v>3</v>
       </c>
       <c r="C203" s="117" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D203" s="96" t="str">
         <f t="shared" si="14"/>
@@ -39963,7 +39963,7 @@
         <v>35</v>
       </c>
       <c r="F203" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G203" s="97">
         <v>1</v>
@@ -40030,7 +40030,7 @@
         <v>1</v>
       </c>
       <c r="C204" s="117" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D204" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40075,7 +40075,7 @@
         <v>2</v>
       </c>
       <c r="C205" s="117" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D205" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40085,7 +40085,7 @@
         <v>35</v>
       </c>
       <c r="F205" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G205" s="97">
         <v>1</v>
@@ -40101,7 +40101,7 @@
         <v>98</v>
       </c>
       <c r="M205" s="118" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N205" s="108">
         <v>3417</v>
@@ -40171,7 +40171,7 @@
         <v>2</v>
       </c>
       <c r="C206" s="117" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D206" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40181,7 +40181,7 @@
         <v>35</v>
       </c>
       <c r="F206" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G206" s="97">
         <v>1</v>
@@ -40197,7 +40197,7 @@
         <v>98</v>
       </c>
       <c r="M206" s="118" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N206" s="108">
         <v>3417</v>
@@ -40267,7 +40267,7 @@
         <v>2</v>
       </c>
       <c r="C207" s="117" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D207" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40277,7 +40277,7 @@
         <v>35</v>
       </c>
       <c r="F207" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G207" s="97">
         <v>1</v>
@@ -40293,7 +40293,7 @@
         <v>98</v>
       </c>
       <c r="M207" s="118" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N207" s="108">
         <v>3417</v>
@@ -40370,7 +40370,7 @@
         <v>2</v>
       </c>
       <c r="C208" s="117" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D208" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40422,7 +40422,7 @@
         <v>3</v>
       </c>
       <c r="C209" s="117" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D209" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40432,7 +40432,7 @@
         <v>35</v>
       </c>
       <c r="F209" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G209" s="97">
         <v>1</v>
@@ -40506,7 +40506,7 @@
         <v>3</v>
       </c>
       <c r="C210" s="117" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D210" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40516,7 +40516,7 @@
         <v>35</v>
       </c>
       <c r="F210" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G210" s="97">
         <v>1</v>
@@ -40530,7 +40530,7 @@
       </c>
       <c r="L210" s="108"/>
       <c r="M210" s="118" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="N210" s="108">
         <v>3417</v>
@@ -40553,7 +40553,7 @@
       <c r="T210" s="108"/>
       <c r="U210" s="108"/>
       <c r="V210" s="108" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W210" s="99" t="s">
         <v>43</v>
@@ -40602,7 +40602,7 @@
         <v>3</v>
       </c>
       <c r="C211" s="117" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D211" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40612,7 +40612,7 @@
         <v>35</v>
       </c>
       <c r="F211" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G211" s="97">
         <v>1</v>
@@ -40628,7 +40628,7 @@
         <v>80</v>
       </c>
       <c r="M211" s="118" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="N211" s="108">
         <v>201049.28</v>
@@ -40647,13 +40647,13 @@
       </c>
       <c r="S211" s="118"/>
       <c r="T211" s="108" t="s">
+        <v>649</v>
+      </c>
+      <c r="U211" s="119" t="s">
         <v>650</v>
       </c>
-      <c r="U211" s="119" t="s">
+      <c r="V211" s="108" t="s">
         <v>651</v>
-      </c>
-      <c r="V211" s="108" t="s">
-        <v>652</v>
       </c>
       <c r="W211" s="99" t="s">
         <v>43</v>
@@ -40702,7 +40702,7 @@
         <v>3</v>
       </c>
       <c r="C212" s="117" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D212" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40712,7 +40712,7 @@
         <v>35</v>
       </c>
       <c r="F212" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G212" s="97">
         <v>1</v>
@@ -40779,7 +40779,7 @@
         <v>2</v>
       </c>
       <c r="C213" s="117" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D213" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40824,7 +40824,7 @@
         <v>3</v>
       </c>
       <c r="C214" s="117" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D214" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40834,7 +40834,7 @@
         <v>35</v>
       </c>
       <c r="F214" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G214" s="97">
         <v>1</v>
@@ -40901,7 +40901,7 @@
         <v>3</v>
       </c>
       <c r="C215" s="117" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D215" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40911,7 +40911,7 @@
         <v>35</v>
       </c>
       <c r="F215" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G215" s="97">
         <v>0.1</v>
@@ -40978,7 +40978,7 @@
         <v>3</v>
       </c>
       <c r="C216" s="117" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D216" s="96" t="str">
         <f t="shared" si="14"/>
@@ -40988,7 +40988,7 @@
         <v>35</v>
       </c>
       <c r="F216" s="96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G216" s="97">
         <v>0.1</v>
@@ -41055,7 +41055,7 @@
         <v>2</v>
       </c>
       <c r="C217" s="117" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D217" s="96" t="str">
         <f t="shared" si="14"/>
@@ -41100,7 +41100,7 @@
         <v>3</v>
       </c>
       <c r="C218" s="117" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D218" s="96" t="str">
         <f t="shared" si="14"/>
@@ -41110,7 +41110,7 @@
         <v>35</v>
       </c>
       <c r="F218" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G218" s="97">
         <v>1</v>
@@ -41177,7 +41177,7 @@
         <v>3</v>
       </c>
       <c r="C219" s="117" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D219" s="96" t="str">
         <f t="shared" si="14"/>
@@ -41187,7 +41187,7 @@
         <v>35</v>
       </c>
       <c r="F219" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G219" s="97">
         <v>1</v>
@@ -41254,7 +41254,7 @@
         <v>3</v>
       </c>
       <c r="C220" s="117" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D220" s="96" t="str">
         <f t="shared" si="14"/>
@@ -41264,7 +41264,7 @@
         <v>35</v>
       </c>
       <c r="F220" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G220" s="97">
         <v>1</v>
@@ -41331,7 +41331,7 @@
         <v>3</v>
       </c>
       <c r="C221" s="117" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D221" s="96" t="str">
         <f t="shared" si="14"/>
@@ -41341,7 +41341,7 @@
         <v>35</v>
       </c>
       <c r="F221" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G221" s="97">
         <v>1</v>
@@ -41408,7 +41408,7 @@
         <v>3</v>
       </c>
       <c r="C222" s="117" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D222" s="96" t="str">
         <f t="shared" si="14"/>
@@ -41418,7 +41418,7 @@
         <v>35</v>
       </c>
       <c r="F222" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G222" s="97">
         <v>1</v>
@@ -41485,7 +41485,7 @@
         <v>3</v>
       </c>
       <c r="C223" s="117" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D223" s="96" t="str">
         <f t="shared" si="14"/>
@@ -41495,7 +41495,7 @@
         <v>35</v>
       </c>
       <c r="F223" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G223" s="97">
         <v>1</v>
@@ -41617,7 +41617,7 @@
         <v>35</v>
       </c>
       <c r="F225" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G225" s="97">
         <v>1</v>
@@ -41633,7 +41633,7 @@
         <v>50</v>
       </c>
       <c r="M225" s="103" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N225" s="108">
         <v>1144</v>
@@ -41650,10 +41650,10 @@
       <c r="R225" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="S225" s="162" t="s">
+      <c r="S225" s="164" t="s">
         <v>340</v>
       </c>
-      <c r="T225" s="162" t="s">
+      <c r="T225" s="164" t="s">
         <v>341</v>
       </c>
       <c r="U225" s="108"/>
@@ -41703,7 +41703,7 @@
         <v>35</v>
       </c>
       <c r="F226" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G226" s="97">
         <v>1</v>
@@ -41719,7 +41719,7 @@
         <v>50</v>
       </c>
       <c r="M226" s="103" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N226" s="108">
         <v>1144</v>
@@ -41792,7 +41792,7 @@
         <v>35</v>
       </c>
       <c r="F227" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G227" s="97">
         <v>1</v>
@@ -41808,7 +41808,7 @@
         <v>50</v>
       </c>
       <c r="M227" s="103" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N227" s="108">
         <v>1144</v>
@@ -41881,7 +41881,7 @@
         <v>35</v>
       </c>
       <c r="F228" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G228" s="97">
         <v>1</v>
@@ -41897,7 +41897,7 @@
         <v>50</v>
       </c>
       <c r="M228" s="103" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N228" s="108">
         <v>1144</v>
@@ -41963,7 +41963,7 @@
         <v>35</v>
       </c>
       <c r="F229" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G229" s="97">
         <v>1</v>
@@ -41979,7 +41979,7 @@
         <v>50</v>
       </c>
       <c r="M229" s="103" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N229" s="108">
         <v>1144</v>
@@ -42045,7 +42045,7 @@
         <v>35</v>
       </c>
       <c r="F230" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G230" s="97">
         <v>1</v>
@@ -42061,7 +42061,7 @@
         <v>50</v>
       </c>
       <c r="M230" s="103" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N230" s="108">
         <v>1144</v>
@@ -42117,7 +42117,7 @@
         <v>1</v>
       </c>
       <c r="C231" s="118" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D231" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42162,7 +42162,7 @@
         <v>2</v>
       </c>
       <c r="C232" s="118" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D232" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42172,7 +42172,7 @@
         <v>35</v>
       </c>
       <c r="F232" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G232" s="97">
         <v>1</v>
@@ -42239,7 +42239,7 @@
         <v>1</v>
       </c>
       <c r="C233" s="118" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D233" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42284,7 +42284,7 @@
         <v>2</v>
       </c>
       <c r="C234" s="118" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D234" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42329,7 +42329,7 @@
         <v>3</v>
       </c>
       <c r="C235" s="118" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D235" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42339,7 +42339,7 @@
         <v>35</v>
       </c>
       <c r="F235" s="96" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G235" s="97">
         <v>1</v>
@@ -42406,7 +42406,7 @@
         <v>2</v>
       </c>
       <c r="C236" s="118" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D236" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42451,7 +42451,7 @@
         <v>3</v>
       </c>
       <c r="C237" s="118" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D237" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42461,7 +42461,7 @@
         <v>35</v>
       </c>
       <c r="F237" s="96" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G237" s="97">
         <v>1</v>
@@ -42528,7 +42528,7 @@
         <v>3</v>
       </c>
       <c r="C238" s="118" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D238" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42538,7 +42538,7 @@
         <v>35</v>
       </c>
       <c r="F238" s="96" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G238" s="97">
         <v>1</v>
@@ -42605,7 +42605,7 @@
         <v>3</v>
       </c>
       <c r="C239" s="118" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D239" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42615,7 +42615,7 @@
         <v>35</v>
       </c>
       <c r="F239" s="96" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G239" s="97">
         <v>1</v>
@@ -42682,7 +42682,7 @@
         <v>2</v>
       </c>
       <c r="C240" s="118" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D240" s="96" t="str">
         <f t="shared" si="14"/>
@@ -42692,7 +42692,7 @@
         <v>35</v>
       </c>
       <c r="F240" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G240" s="97">
         <v>1</v>
@@ -42818,7 +42818,7 @@
         <v>35</v>
       </c>
       <c r="F242" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G242" s="97">
         <v>1</v>
@@ -42876,7 +42876,7 @@
         <v>35</v>
       </c>
       <c r="F243" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G243" s="97">
         <v>1</v>
@@ -42940,7 +42940,7 @@
         <v>35</v>
       </c>
       <c r="F244" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G244" s="97">
         <v>1</v>
@@ -42997,7 +42997,7 @@
         <v>35</v>
       </c>
       <c r="F245" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G245" s="97">
         <v>1</v>
@@ -43054,7 +43054,7 @@
         <v>35</v>
       </c>
       <c r="F246" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G246" s="97">
         <v>1</v>
@@ -43107,7 +43107,7 @@
         <v>35</v>
       </c>
       <c r="F247" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G247" s="97">
         <v>1</v>
@@ -43213,7 +43213,7 @@
         <v>35</v>
       </c>
       <c r="F249" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G249" s="97">
         <v>1</v>
@@ -43448,7 +43448,7 @@
         <v>382</v>
       </c>
       <c r="M253" s="118" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N253" s="108"/>
       <c r="O253" s="108"/>
@@ -43535,7 +43535,7 @@
         <v>382</v>
       </c>
       <c r="M254" s="118" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N254" s="108"/>
       <c r="O254" s="108"/>
@@ -43648,7 +43648,7 @@
         <v>2</v>
       </c>
       <c r="C256" s="117" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D256" s="96" t="str">
         <f t="shared" si="32"/>
@@ -43695,7 +43695,7 @@
         <v>2</v>
       </c>
       <c r="C257" s="117" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D257" s="96" t="str">
         <f t="shared" si="32"/>
@@ -43742,7 +43742,7 @@
         <v>1</v>
       </c>
       <c r="C258" s="117" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D258" s="96" t="str">
         <f t="shared" si="32"/>
@@ -43787,7 +43787,7 @@
         <v>2</v>
       </c>
       <c r="C259" s="117" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D259" s="96" t="str">
         <f t="shared" si="32"/>
@@ -43832,7 +43832,7 @@
         <v>2</v>
       </c>
       <c r="C260" s="117" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D260" s="96" t="str">
         <f t="shared" si="32"/>
@@ -43877,7 +43877,7 @@
         <v>3</v>
       </c>
       <c r="C261" s="117" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D261" s="96" t="str">
         <f t="shared" si="32"/>
@@ -43887,7 +43887,7 @@
         <v>35</v>
       </c>
       <c r="F261" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G261" s="97">
         <v>1</v>
@@ -43952,7 +43952,7 @@
         <v>3</v>
       </c>
       <c r="C262" s="117" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D262" s="96" t="str">
         <f t="shared" si="32"/>
@@ -43997,7 +43997,7 @@
         <v>4</v>
       </c>
       <c r="C263" s="117" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D263" s="96" t="str">
         <f t="shared" si="32"/>
@@ -44007,7 +44007,7 @@
         <v>35</v>
       </c>
       <c r="F263" s="96" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G263" s="97">
         <v>1</v>
@@ -44030,12 +44030,12 @@
         <v>153</v>
       </c>
       <c r="S263" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T263" s="120"/>
       <c r="U263" s="119"/>
       <c r="V263" s="108" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="W263" s="99"/>
       <c r="X263" s="109">
@@ -44080,7 +44080,7 @@
         <v>4</v>
       </c>
       <c r="C264" s="117" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D264" s="96" t="str">
         <f t="shared" si="32"/>
@@ -44090,7 +44090,7 @@
         <v>35</v>
       </c>
       <c r="F264" s="96" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G264" s="97">
         <v>1</v>
@@ -44113,7 +44113,7 @@
         <v>153</v>
       </c>
       <c r="S264" s="118" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="T264" s="120"/>
       <c r="U264" s="119"/>
@@ -44161,7 +44161,7 @@
         <v>4</v>
       </c>
       <c r="C265" s="117" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D265" s="96" t="str">
         <f t="shared" si="32"/>
@@ -44171,7 +44171,7 @@
         <v>35</v>
       </c>
       <c r="F265" s="96" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G265" s="97">
         <v>1</v>
@@ -44194,12 +44194,12 @@
         <v>153</v>
       </c>
       <c r="S265" s="118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T265" s="120"/>
       <c r="U265" s="119"/>
       <c r="V265" s="108" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="W265" s="99"/>
       <c r="X265" s="109">
@@ -44244,7 +44244,7 @@
         <v>3</v>
       </c>
       <c r="C266" s="117" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D266" s="96" t="str">
         <f t="shared" si="32"/>
@@ -44254,7 +44254,7 @@
         <v>35</v>
       </c>
       <c r="F266" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G266" s="97">
         <v>1</v>
@@ -44339,7 +44339,7 @@
         <v>1</v>
       </c>
       <c r="C267" s="117" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D267" s="96" t="str">
         <f t="shared" si="32"/>
@@ -44384,7 +44384,7 @@
         <v>1</v>
       </c>
       <c r="C268" s="117" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D268" s="96" t="str">
         <f t="shared" si="32"/>
@@ -44422,19 +44422,47 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="S242:S245"/>
-    <mergeCell ref="U33:U35"/>
-    <mergeCell ref="U98:U100"/>
-    <mergeCell ref="U67:U69"/>
-    <mergeCell ref="U117:U119"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="U79:U81"/>
-    <mergeCell ref="U38:U40"/>
-    <mergeCell ref="U112:U114"/>
-    <mergeCell ref="T122:T124"/>
-    <mergeCell ref="S67:S69"/>
-    <mergeCell ref="T67:T69"/>
-    <mergeCell ref="T127:T129"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="S225:S230"/>
+    <mergeCell ref="S122:S124"/>
+    <mergeCell ref="U57:U59"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="U62:U64"/>
+    <mergeCell ref="T117:T119"/>
+    <mergeCell ref="S112:S114"/>
+    <mergeCell ref="S57:S59"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="U28:U30"/>
+    <mergeCell ref="U93:U95"/>
+    <mergeCell ref="S127:S129"/>
+    <mergeCell ref="T225:T230"/>
+    <mergeCell ref="S74:S76"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T74:T76"/>
+    <mergeCell ref="T112:T114"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="S117:S119"/>
+    <mergeCell ref="U45:U47"/>
+    <mergeCell ref="T93:T95"/>
+    <mergeCell ref="S98:S100"/>
+    <mergeCell ref="S105:S107"/>
+    <mergeCell ref="U74:U76"/>
+    <mergeCell ref="T62:T64"/>
+    <mergeCell ref="U105:U107"/>
+    <mergeCell ref="T38:T40"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S86:S88"/>
+    <mergeCell ref="U86:U88"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T33:T35"/>
+    <mergeCell ref="T18:T20"/>
+    <mergeCell ref="T98:T100"/>
+    <mergeCell ref="T45:T47"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="S18:S20"/>
     <mergeCell ref="U122:U124"/>
     <mergeCell ref="U18:U20"/>
@@ -44451,47 +44479,19 @@
     <mergeCell ref="T28:T30"/>
     <mergeCell ref="S45:S47"/>
     <mergeCell ref="S79:S81"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T33:T35"/>
-    <mergeCell ref="T18:T20"/>
-    <mergeCell ref="T98:T100"/>
-    <mergeCell ref="T45:T47"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T74:T76"/>
-    <mergeCell ref="T112:T114"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="S117:S119"/>
-    <mergeCell ref="U45:U47"/>
-    <mergeCell ref="T93:T95"/>
-    <mergeCell ref="S98:S100"/>
-    <mergeCell ref="S105:S107"/>
-    <mergeCell ref="U74:U76"/>
-    <mergeCell ref="T62:T64"/>
-    <mergeCell ref="U105:U107"/>
-    <mergeCell ref="T38:T40"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S86:S88"/>
-    <mergeCell ref="U86:U88"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="S225:S230"/>
-    <mergeCell ref="S122:S124"/>
-    <mergeCell ref="U57:U59"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="U62:U64"/>
-    <mergeCell ref="T117:T119"/>
-    <mergeCell ref="S112:S114"/>
-    <mergeCell ref="S57:S59"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="U28:U30"/>
-    <mergeCell ref="U93:U95"/>
-    <mergeCell ref="S127:S129"/>
-    <mergeCell ref="T225:T230"/>
-    <mergeCell ref="S74:S76"/>
+    <mergeCell ref="S242:S245"/>
+    <mergeCell ref="U33:U35"/>
+    <mergeCell ref="U98:U100"/>
+    <mergeCell ref="U67:U69"/>
+    <mergeCell ref="U117:U119"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="U79:U81"/>
+    <mergeCell ref="U38:U40"/>
+    <mergeCell ref="U112:U114"/>
+    <mergeCell ref="T122:T124"/>
+    <mergeCell ref="S67:S69"/>
+    <mergeCell ref="T67:T69"/>
+    <mergeCell ref="T127:T129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
